--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>207600</v>
+        <v>287900</v>
       </c>
       <c r="E8" s="3">
-        <v>210900</v>
+        <v>200300</v>
       </c>
       <c r="F8" s="3">
-        <v>207700</v>
+        <v>213300</v>
       </c>
       <c r="G8" s="3">
+        <v>216800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>213500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>183200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>151100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>189600</v>
+      </c>
+      <c r="L8" s="3">
+        <v>230000</v>
+      </c>
+      <c r="M8" s="3">
+        <v>160300</v>
+      </c>
+      <c r="N8" s="3">
+        <v>116600</v>
+      </c>
+      <c r="O8" s="3">
+        <v>141100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>202500</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>128900</v>
+      </c>
+      <c r="R8" s="3">
+        <v>99400</v>
+      </c>
+      <c r="S8" s="3">
+        <v>164700</v>
+      </c>
+      <c r="T8" s="3">
+        <v>229800</v>
+      </c>
+      <c r="U8" s="3">
+        <v>184700</v>
+      </c>
+      <c r="V8" s="3">
+        <v>185900</v>
+      </c>
+      <c r="W8" s="3">
+        <v>202500</v>
+      </c>
+      <c r="X8" s="3">
+        <v>275500</v>
+      </c>
+      <c r="Y8" s="3">
         <v>178300</v>
       </c>
-      <c r="H8" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>189600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>230000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>160300</v>
-      </c>
-      <c r="L8" s="3">
-        <v>116600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>141100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>202500</v>
-      </c>
-      <c r="O8" s="3">
-        <v>128900</v>
-      </c>
-      <c r="P8" s="3">
-        <v>99400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>164700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>229800</v>
-      </c>
-      <c r="S8" s="3">
-        <v>184700</v>
-      </c>
-      <c r="T8" s="3">
-        <v>185900</v>
-      </c>
-      <c r="U8" s="3">
-        <v>202500</v>
-      </c>
-      <c r="V8" s="3">
-        <v>275500</v>
-      </c>
-      <c r="W8" s="3">
-        <v>178300</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>157200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>190200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>231400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>187400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>229400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>167500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>207900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,8 +975,14 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1070,14 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,13 +1295,19 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1280,168 +1319,180 @@
         <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>18200</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
+        <v>18700</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>12400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>4600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>1600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>25900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>59500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>57600</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F15" s="3">
-        <v>60300</v>
+        <v>61100</v>
       </c>
       <c r="G15" s="3">
-        <v>54100</v>
+        <v>59200</v>
       </c>
       <c r="H15" s="3">
-        <v>51800</v>
+        <v>61900</v>
       </c>
       <c r="I15" s="3">
+        <v>55600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>53200</v>
+      </c>
+      <c r="K15" s="3">
         <v>53300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>52400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>49200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>41400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>41200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>42300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>41800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>42400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>48000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>47600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>48900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>47000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>44300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>48100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>50100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>45800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>45300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>52300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>50400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>41500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>42900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>48800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1521,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>207900</v>
+        <v>252800</v>
       </c>
       <c r="E17" s="3">
-        <v>216800</v>
+        <v>198000</v>
       </c>
       <c r="F17" s="3">
-        <v>211200</v>
+        <v>213700</v>
       </c>
       <c r="G17" s="3">
-        <v>182400</v>
+        <v>222800</v>
       </c>
       <c r="H17" s="3">
-        <v>222400</v>
+        <v>217100</v>
       </c>
       <c r="I17" s="3">
+        <v>187500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>228600</v>
+      </c>
+      <c r="K17" s="3">
         <v>216700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>223400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>173100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>162200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>166800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>145700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>161000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>146900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>169100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>180000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>169700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>217300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>183500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>217400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>160000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>187500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>180800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>176400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>164000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>175800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>172900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>158300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3500</v>
-      </c>
       <c r="G18" s="3">
-        <v>-4100</v>
+        <v>-6000</v>
       </c>
       <c r="H18" s="3">
-        <v>-75400</v>
+        <v>-3600</v>
       </c>
       <c r="I18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-77500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-27100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-45600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-25700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>56800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-32000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-47500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>49800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-31400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>58100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>18300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>9400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>55000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>23400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>53600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>49600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,453 +1746,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>11100</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>9800</v>
+        <v>-44100</v>
       </c>
       <c r="F20" s="3">
-        <v>25100</v>
+        <v>11400</v>
       </c>
       <c r="G20" s="3">
-        <v>-29500</v>
+        <v>10100</v>
       </c>
       <c r="H20" s="3">
-        <v>-29000</v>
+        <v>25800</v>
       </c>
       <c r="I20" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-10500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>28800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-26700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>27300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>7000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>70200</v>
+        <v>39400</v>
       </c>
       <c r="E21" s="3">
-        <v>61500</v>
+        <v>23100</v>
       </c>
       <c r="F21" s="3">
-        <v>81900</v>
+        <v>72100</v>
       </c>
       <c r="G21" s="3">
-        <v>20400</v>
+        <v>63200</v>
       </c>
       <c r="H21" s="3">
-        <v>-52600</v>
+        <v>84200</v>
       </c>
       <c r="I21" s="3">
+        <v>21000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="K21" s="3">
         <v>15700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>56400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>30800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>19900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>128000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>16900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>124600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>60000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>12000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>65400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>104800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>68200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>4200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>61600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>108000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>79400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>98100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>39700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>89700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>12900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>11000</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F22" s="3">
-        <v>10100</v>
+        <v>13300</v>
       </c>
       <c r="G22" s="3">
-        <v>9000</v>
+        <v>11300</v>
       </c>
       <c r="H22" s="3">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="I22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>6600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>6700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>6700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>6100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>6200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>6500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>5600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>6400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>6700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>7000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>6500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>7100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2200</v>
+        <v>34700</v>
       </c>
       <c r="E23" s="3">
-        <v>-7000</v>
+        <v>-41800</v>
       </c>
       <c r="F23" s="3">
-        <v>11500</v>
+        <v>-2300</v>
       </c>
       <c r="G23" s="3">
-        <v>-42600</v>
+        <v>-7200</v>
       </c>
       <c r="H23" s="3">
-        <v>-113900</v>
+        <v>11800</v>
       </c>
       <c r="I23" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-117100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-44500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-25100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-52200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-27500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>79800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-32000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-56800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-38000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>70600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-42500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>14800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>49700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>11600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-48300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>10700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>49300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>22300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>49600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>33800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1400</v>
+        <v>8700</v>
       </c>
       <c r="E24" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-9700</v>
-      </c>
       <c r="H24" s="3">
-        <v>-26000</v>
+        <v>3800</v>
       </c>
       <c r="I24" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="K24" s="3">
         <v>-10200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-5400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-8500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-13700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>17400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-11100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>4600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>14400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>11100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>9900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>10700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3600</v>
+        <v>26000</v>
       </c>
       <c r="E26" s="3">
-        <v>-6900</v>
+        <v>-32800</v>
       </c>
       <c r="F26" s="3">
-        <v>7800</v>
+        <v>-3700</v>
       </c>
       <c r="G26" s="3">
-        <v>-32900</v>
+        <v>-7100</v>
       </c>
       <c r="H26" s="3">
-        <v>-87900</v>
+        <v>8000</v>
       </c>
       <c r="I26" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-34400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-19700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-53700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-18900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>84000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-31900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-24300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>53200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-31400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>35400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>8800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>8900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>38200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>12500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>31600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>23100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3600</v>
+        <v>26000</v>
       </c>
       <c r="E27" s="3">
-        <v>-6900</v>
+        <v>-32800</v>
       </c>
       <c r="F27" s="3">
-        <v>7800</v>
+        <v>-3700</v>
       </c>
       <c r="G27" s="3">
-        <v>-32900</v>
+        <v>-7100</v>
       </c>
       <c r="H27" s="3">
-        <v>-87900</v>
+        <v>8000</v>
       </c>
       <c r="I27" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-34400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-19700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-53700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-18900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>84000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-31900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-24300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>53200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-31400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>10200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>35400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>8800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>8900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>38200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>12500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>31600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>23100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,28 +2597,34 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2512,56 +2633,56 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-79900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-2700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-9200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-3900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>1000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-6200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-5400</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2882,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-11100</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>-9800</v>
+        <v>44100</v>
       </c>
       <c r="F32" s="3">
-        <v>-25100</v>
+        <v>-11400</v>
       </c>
       <c r="G32" s="3">
-        <v>29500</v>
+        <v>-10100</v>
       </c>
       <c r="H32" s="3">
-        <v>29000</v>
+        <v>-25800</v>
       </c>
       <c r="I32" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K32" s="3">
         <v>10500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-28800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>26700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-27300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>11200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>8700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3600</v>
+        <v>26000</v>
       </c>
       <c r="E33" s="3">
-        <v>-6900</v>
+        <v>-32800</v>
       </c>
       <c r="F33" s="3">
-        <v>7800</v>
+        <v>-3700</v>
       </c>
       <c r="G33" s="3">
-        <v>-32900</v>
+        <v>-7100</v>
       </c>
       <c r="H33" s="3">
-        <v>-87900</v>
+        <v>8000</v>
       </c>
       <c r="I33" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-34400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-19700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-133600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-21600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>74800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-35800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-30400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>47700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-31400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>10200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>35400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>8800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>8900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>12500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>31600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>23100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3600</v>
+        <v>26000</v>
       </c>
       <c r="E35" s="3">
-        <v>-6900</v>
+        <v>-32800</v>
       </c>
       <c r="F35" s="3">
-        <v>7800</v>
+        <v>-3700</v>
       </c>
       <c r="G35" s="3">
-        <v>-32900</v>
+        <v>-7100</v>
       </c>
       <c r="H35" s="3">
-        <v>-87900</v>
+        <v>8000</v>
       </c>
       <c r="I35" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-34400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-19700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-133600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-21600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>74800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-35800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-30400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>47700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-31400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>10200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>35400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>8800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>8900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>12500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>31600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>23100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3436,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>94300</v>
+        <v>80100</v>
       </c>
       <c r="E41" s="3">
-        <v>91500</v>
+        <v>103100</v>
       </c>
       <c r="F41" s="3">
-        <v>38500</v>
+        <v>96900</v>
       </c>
       <c r="G41" s="3">
-        <v>30100</v>
+        <v>94000</v>
       </c>
       <c r="H41" s="3">
-        <v>150400</v>
+        <v>39600</v>
       </c>
       <c r="I41" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>154600</v>
+      </c>
+      <c r="K41" s="3">
         <v>118800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>108500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>125000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>137300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>101000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>94400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>69700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>62900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>120100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>137500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>191300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>435300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>258100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>251500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>326900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>312900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>209100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>202600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>282000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>378600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>201000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>161600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,631 +3622,679 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>111300</v>
+        <v>185200</v>
       </c>
       <c r="E43" s="3">
-        <v>160800</v>
+        <v>112100</v>
       </c>
       <c r="F43" s="3">
-        <v>219400</v>
+        <v>114400</v>
       </c>
       <c r="G43" s="3">
-        <v>128800</v>
+        <v>165300</v>
       </c>
       <c r="H43" s="3">
-        <v>113600</v>
+        <v>225500</v>
       </c>
       <c r="I43" s="3">
+        <v>132400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>116800</v>
+      </c>
+      <c r="K43" s="3">
         <v>129200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>156100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>107000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>114800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>101500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>152600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>116300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>199300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>113300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>144100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>125300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>92300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>247800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>164900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>122400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>218300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>152200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>160500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>111200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>135300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>114100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>163800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3900</v>
+        <v>5100</v>
       </c>
       <c r="E44" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K44" s="3">
         <v>3300</v>
       </c>
-      <c r="F44" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R44" s="3">
         <v>2700</v>
       </c>
-      <c r="I44" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="S44" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U44" s="3">
         <v>3600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="V44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Y44" s="3">
         <v>3500</v>
       </c>
-      <c r="L44" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="N44" s="3">
-        <v>3300</v>
-      </c>
-      <c r="O44" s="3">
-        <v>4200</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Z44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AC44" s="3">
         <v>2700</v>
       </c>
-      <c r="Q44" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="S44" s="3">
-        <v>3600</v>
-      </c>
-      <c r="T44" s="3">
-        <v>3000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="V44" s="3">
-        <v>3400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="AD44" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>30800</v>
+        <v>37500</v>
       </c>
       <c r="E45" s="3">
-        <v>27900</v>
+        <v>54900</v>
       </c>
       <c r="F45" s="3">
-        <v>42100</v>
+        <v>31600</v>
       </c>
       <c r="G45" s="3">
-        <v>53400</v>
+        <v>28700</v>
       </c>
       <c r="H45" s="3">
-        <v>27500</v>
+        <v>43300</v>
       </c>
       <c r="I45" s="3">
+        <v>54900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>28200</v>
+      </c>
+      <c r="K45" s="3">
         <v>27000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>27300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>34300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>21000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>25700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>9400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>15400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>18000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>21400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>18900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>700</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>700</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>4200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>5200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>6000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>240300</v>
+        <v>307900</v>
       </c>
       <c r="E46" s="3">
-        <v>283500</v>
+        <v>276500</v>
       </c>
       <c r="F46" s="3">
-        <v>304100</v>
+        <v>247000</v>
       </c>
       <c r="G46" s="3">
-        <v>217000</v>
+        <v>291400</v>
       </c>
       <c r="H46" s="3">
-        <v>294200</v>
+        <v>312500</v>
       </c>
       <c r="I46" s="3">
+        <v>223000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>302400</v>
+      </c>
+      <c r="K46" s="3">
         <v>278400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>295400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>269900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>264200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>221400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>271400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>215800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>274200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>252100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>303100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>341700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>549500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>509300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>420600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>453500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>534500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>366700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>369100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>399100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>520200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>322100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>332900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>27700</v>
+        <v>31200</v>
       </c>
       <c r="E47" s="3">
-        <v>26700</v>
+        <v>57400</v>
       </c>
       <c r="F47" s="3">
-        <v>26300</v>
+        <v>28400</v>
       </c>
       <c r="G47" s="3">
-        <v>24000</v>
+        <v>27400</v>
       </c>
       <c r="H47" s="3">
-        <v>36900</v>
+        <v>27100</v>
       </c>
       <c r="I47" s="3">
+        <v>24600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K47" s="3">
         <v>43900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>50900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>54200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>25300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>31500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>40200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>29700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>53300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>56500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>55400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>57100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>14000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>14000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>14400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>14100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>6800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>8600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>16200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>13000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>20100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>19700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>5600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>349900</v>
+        <v>361200</v>
       </c>
       <c r="E48" s="3">
-        <v>329700</v>
+        <v>363800</v>
       </c>
       <c r="F48" s="3">
-        <v>331100</v>
+        <v>359600</v>
       </c>
       <c r="G48" s="3">
-        <v>333100</v>
+        <v>338900</v>
       </c>
       <c r="H48" s="3">
-        <v>331200</v>
+        <v>340300</v>
       </c>
       <c r="I48" s="3">
+        <v>342400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>340500</v>
+      </c>
+      <c r="K48" s="3">
         <v>333200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>335000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>344400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>337500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>327100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>323100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>328800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>341400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>378900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>386600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>384000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>383500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>346300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>344300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>345200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>353000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>352800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>661600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>340100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>337400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>339900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>339900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1007800</v>
+        <v>1176300</v>
       </c>
       <c r="E49" s="3">
-        <v>1046200</v>
+        <v>1232700</v>
       </c>
       <c r="F49" s="3">
-        <v>1081200</v>
+        <v>1035900</v>
       </c>
       <c r="G49" s="3">
-        <v>1142500</v>
+        <v>1075300</v>
       </c>
       <c r="H49" s="3">
-        <v>922100</v>
+        <v>1111300</v>
       </c>
       <c r="I49" s="3">
+        <v>1174300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>947800</v>
+      </c>
+      <c r="K49" s="3">
         <v>963400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1007700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1075800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>936100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>926100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>910700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>923400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>945600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1044600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1034400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1071500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1088000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>956700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>976700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1013600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1033800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>972200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>935900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>931700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4477,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9300</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>18700</v>
+        <v>8200</v>
       </c>
       <c r="F52" s="3">
-        <v>27500</v>
+        <v>9600</v>
       </c>
       <c r="G52" s="3">
-        <v>46300</v>
+        <v>19300</v>
       </c>
       <c r="H52" s="3">
-        <v>20400</v>
+        <v>28300</v>
       </c>
       <c r="I52" s="3">
+        <v>47600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K52" s="3">
         <v>8700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>6500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>74600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>73000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>65500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>73200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>73500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>73500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>75800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>82700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>77000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>79500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>88400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>88100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>104000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>102600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>177500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>186700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>192900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>194100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1635000</v>
+        <v>1877000</v>
       </c>
       <c r="E54" s="3">
-        <v>1704800</v>
+        <v>1938700</v>
       </c>
       <c r="F54" s="3">
-        <v>1770300</v>
+        <v>1680500</v>
       </c>
       <c r="G54" s="3">
-        <v>1762900</v>
+        <v>1752200</v>
       </c>
       <c r="H54" s="3">
-        <v>1604900</v>
+        <v>1819500</v>
       </c>
       <c r="I54" s="3">
+        <v>1812000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1649600</v>
+      </c>
+      <c r="K54" s="3">
         <v>1627600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1694500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1750700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1563800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1580700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1618300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1563300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1687700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1805500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1852900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1930100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2117700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1903300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1835600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1914900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1998400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1786500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4836,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>293400</v>
+        <v>295400</v>
       </c>
       <c r="E57" s="3">
-        <v>292200</v>
+        <v>341400</v>
       </c>
       <c r="F57" s="3">
-        <v>282600</v>
+        <v>301500</v>
       </c>
       <c r="G57" s="3">
-        <v>320600</v>
+        <v>300300</v>
       </c>
       <c r="H57" s="3">
-        <v>273700</v>
+        <v>290400</v>
       </c>
       <c r="I57" s="3">
+        <v>329500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>281300</v>
+      </c>
+      <c r="K57" s="3">
         <v>268200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>257200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>296200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>239100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>215100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>202600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>223300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>263600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>254500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>207400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>233800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>326000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>247300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>238500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>244400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>346500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>270000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>238600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>264200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>248200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>232300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>219500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>132700</v>
+        <v>341300</v>
       </c>
       <c r="E58" s="3">
-        <v>253600</v>
+        <v>261800</v>
       </c>
       <c r="F58" s="3">
-        <v>256900</v>
+        <v>136400</v>
       </c>
       <c r="G58" s="3">
+        <v>260700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>264000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>132500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>136800</v>
+      </c>
+      <c r="K58" s="3">
         <v>128900</v>
       </c>
-      <c r="H58" s="3">
-        <v>133100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>128900</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>131400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>80100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>82400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>75900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>76900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>8100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>9400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>7700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>7300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>11700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>7700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>11900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>8100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>8100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>227500</v>
+        <v>206700</v>
       </c>
       <c r="E59" s="3">
-        <v>177100</v>
+        <v>288400</v>
       </c>
       <c r="F59" s="3">
-        <v>215200</v>
+        <v>233900</v>
       </c>
       <c r="G59" s="3">
-        <v>213900</v>
+        <v>182000</v>
       </c>
       <c r="H59" s="3">
-        <v>207100</v>
+        <v>221200</v>
       </c>
       <c r="I59" s="3">
+        <v>219900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>212900</v>
+      </c>
+      <c r="K59" s="3">
         <v>178500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>198100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>249200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>155000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>146400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>176000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>204700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>214200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>137700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>209000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>285700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>273100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>218600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>178900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>300100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>238400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>99100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>157200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>262900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>279700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>141200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>204600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>653600</v>
+        <v>843400</v>
       </c>
       <c r="E60" s="3">
-        <v>722900</v>
+        <v>891600</v>
       </c>
       <c r="F60" s="3">
-        <v>754600</v>
+        <v>671800</v>
       </c>
       <c r="G60" s="3">
-        <v>663500</v>
+        <v>743000</v>
       </c>
       <c r="H60" s="3">
-        <v>613900</v>
+        <v>775600</v>
       </c>
       <c r="I60" s="3">
+        <v>681900</v>
+      </c>
+      <c r="J60" s="3">
+        <v>631000</v>
+      </c>
+      <c r="K60" s="3">
         <v>575700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>586800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>625400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>476500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>437400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>455500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>431600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>485900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>397500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>425800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>524900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>606900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>468800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>424700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>547500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>596600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>376800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>407800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>535200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>535400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>377100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>432200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>639100</v>
+        <v>655700</v>
       </c>
       <c r="E61" s="3">
-        <v>649900</v>
+        <v>684200</v>
       </c>
       <c r="F61" s="3">
-        <v>667600</v>
+        <v>656900</v>
       </c>
       <c r="G61" s="3">
-        <v>719500</v>
+        <v>668000</v>
       </c>
       <c r="H61" s="3">
-        <v>661500</v>
+        <v>686200</v>
       </c>
       <c r="I61" s="3">
+        <v>739500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>679900</v>
+      </c>
+      <c r="K61" s="3">
         <v>610600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>595500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>607200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>580900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>559600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>555500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>592100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>638400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>692800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>668900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>717900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>715700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>656800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>663800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>650400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>629200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>590800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>619200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>623500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>649100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>679800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>692400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>213300</v>
+        <v>255500</v>
       </c>
       <c r="E62" s="3">
-        <v>202300</v>
+        <v>271100</v>
       </c>
       <c r="F62" s="3">
-        <v>211900</v>
+        <v>219200</v>
       </c>
       <c r="G62" s="3">
-        <v>254400</v>
+        <v>207900</v>
       </c>
       <c r="H62" s="3">
-        <v>171300</v>
+        <v>217800</v>
       </c>
       <c r="I62" s="3">
+        <v>261500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>176100</v>
+      </c>
+      <c r="K62" s="3">
         <v>178900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>206000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>205400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>168300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>131100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>132100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>138100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>134900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>164000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>129500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>127200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>207600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>173500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>149100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>145800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>220400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>189900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>181100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>172900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>189700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>146700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>150200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1506100</v>
+        <v>1754500</v>
       </c>
       <c r="E66" s="3">
-        <v>1575100</v>
+        <v>1846900</v>
       </c>
       <c r="F66" s="3">
-        <v>1634100</v>
+        <v>1548000</v>
       </c>
       <c r="G66" s="3">
-        <v>1637300</v>
+        <v>1618900</v>
       </c>
       <c r="H66" s="3">
-        <v>1446700</v>
+        <v>1679600</v>
       </c>
       <c r="I66" s="3">
+        <v>1682900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1365200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1388400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1438100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1225700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1128100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1143200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1161800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1259200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1254400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1224200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1370000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1530200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1299100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1237600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1343700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1446200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1157500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>65000</v>
+        <v>61800</v>
       </c>
       <c r="E72" s="3">
-        <v>68200</v>
+        <v>34900</v>
       </c>
       <c r="F72" s="3">
-        <v>74400</v>
+        <v>66800</v>
       </c>
       <c r="G72" s="3">
-        <v>65800</v>
+        <v>70100</v>
       </c>
       <c r="H72" s="3">
-        <v>98000</v>
+        <v>76400</v>
       </c>
       <c r="I72" s="3">
+        <v>67600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>100700</v>
+      </c>
+      <c r="K72" s="3">
         <v>202400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>259000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>265800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>292100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>409300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>435200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>363400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>410200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>511700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>570600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>522500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>540400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>553600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>554200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>518600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>498700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>556100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>565500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>590400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>577100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>562200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>582100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>129000</v>
+        <v>122400</v>
       </c>
       <c r="E76" s="3">
-        <v>129700</v>
+        <v>91800</v>
       </c>
       <c r="F76" s="3">
-        <v>136200</v>
+        <v>132500</v>
       </c>
       <c r="G76" s="3">
-        <v>125600</v>
+        <v>133300</v>
       </c>
       <c r="H76" s="3">
-        <v>158200</v>
+        <v>139900</v>
       </c>
       <c r="I76" s="3">
+        <v>129100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>162600</v>
+      </c>
+      <c r="K76" s="3">
         <v>262400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>306100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>312600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>338100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>452600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>475100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>401400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>428500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>551100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>628700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>560000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>587600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>604200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>598000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>571200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>552200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>629000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>624100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>649100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>626200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>602800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>615800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3600</v>
+        <v>26000</v>
       </c>
       <c r="E81" s="3">
-        <v>-6900</v>
+        <v>-32800</v>
       </c>
       <c r="F81" s="3">
-        <v>7800</v>
+        <v>-3700</v>
       </c>
       <c r="G81" s="3">
-        <v>-32900</v>
+        <v>-7100</v>
       </c>
       <c r="H81" s="3">
-        <v>-87900</v>
+        <v>8000</v>
       </c>
       <c r="I81" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-34400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-19700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-133600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-21600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>74800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-35800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-30400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>47700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-31400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>10200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>35400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>8800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>8900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>12500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>31600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>23100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7001,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>59500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>57600</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F83" s="3">
-        <v>60300</v>
+        <v>61100</v>
       </c>
       <c r="G83" s="3">
-        <v>54100</v>
+        <v>59200</v>
       </c>
       <c r="H83" s="3">
-        <v>51800</v>
+        <v>61900</v>
       </c>
       <c r="I83" s="3">
+        <v>55600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>53200</v>
+      </c>
+      <c r="K83" s="3">
         <v>53300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>52400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>49200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>41400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>41200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>42300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>41800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>47000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>48000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>47600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>48900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>47000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>44300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>48100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>50100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>45800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>45300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>52300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>50400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>41500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>42900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>48800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>135500</v>
+        <v>-59300</v>
       </c>
       <c r="E89" s="3">
-        <v>67100</v>
+        <v>27400</v>
       </c>
       <c r="F89" s="3">
-        <v>-76300</v>
+        <v>139300</v>
       </c>
       <c r="G89" s="3">
-        <v>-7500</v>
+        <v>68900</v>
       </c>
       <c r="H89" s="3">
-        <v>51000</v>
+        <v>-78400</v>
       </c>
       <c r="I89" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>52400</v>
+      </c>
+      <c r="K89" s="3">
         <v>28800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-39100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>80600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>30800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>32200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>73700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>35000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-20800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-19600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>212500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>29600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-56000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>151600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>130000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>27400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>23400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>231800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>52400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7701,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-17200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-17500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-32600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-104400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-16200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-11100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-20600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-75800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-12900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-6200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-13500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-4300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-6900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-3200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-6500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7982,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6800</v>
+        <v>-39100</v>
       </c>
       <c r="E94" s="3">
-        <v>-14200</v>
+        <v>-147400</v>
       </c>
       <c r="F94" s="3">
-        <v>-37800</v>
+        <v>-7000</v>
       </c>
       <c r="G94" s="3">
-        <v>-115100</v>
+        <v>-14600</v>
       </c>
       <c r="H94" s="3">
-        <v>-7600</v>
+        <v>-38900</v>
       </c>
       <c r="I94" s="3">
+        <v>-118300</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-23100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-82100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-11500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-43600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-63200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-34400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-23100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-220100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-43100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-24500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-143500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>5300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7669,13 +8136,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-14900</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-13500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-15300</v>
       </c>
       <c r="K96" s="3">
         <v>-13500</v>
@@ -7684,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-13500</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7693,55 +8160,61 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-16600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8492,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-124500</v>
+        <v>76100</v>
       </c>
       <c r="E100" s="3">
+        <v>127300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
-        <v>123400</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>126800</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>49100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-13300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>69800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-20100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-16600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-15500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-5000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-14400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1400</v>
+        <v>-700</v>
       </c>
       <c r="E101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J101" s="3">
         <v>3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>5400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-9400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>12000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>8200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-4700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>5100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>9500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2800</v>
+        <v>-23000</v>
       </c>
       <c r="E102" s="3">
-        <v>53000</v>
+        <v>6100</v>
       </c>
       <c r="F102" s="3">
-        <v>8400</v>
+        <v>2900</v>
       </c>
       <c r="G102" s="3">
-        <v>-120300</v>
+        <v>54400</v>
       </c>
       <c r="H102" s="3">
-        <v>31600</v>
+        <v>8600</v>
       </c>
       <c r="I102" s="3">
+        <v>-123600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>32400</v>
+      </c>
+      <c r="K102" s="3">
         <v>10400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-13900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-15200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>32200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>25400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-47200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-14100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-53800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-228200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>161000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-75400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>7200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>103800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>8300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>179500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>39400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -797,25 +797,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>287900</v>
+        <v>288900</v>
       </c>
       <c r="E8" s="3">
-        <v>200300</v>
+        <v>201000</v>
       </c>
       <c r="F8" s="3">
-        <v>213300</v>
+        <v>214100</v>
       </c>
       <c r="G8" s="3">
-        <v>216800</v>
+        <v>217500</v>
       </c>
       <c r="H8" s="3">
-        <v>213500</v>
+        <v>214200</v>
       </c>
       <c r="I8" s="3">
-        <v>183200</v>
+        <v>183900</v>
       </c>
       <c r="J8" s="3">
-        <v>151100</v>
+        <v>151600</v>
       </c>
       <c r="K8" s="3">
         <v>189600</v>
@@ -1325,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="J14" s="3">
-        <v>18700</v>
+        <v>18800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1408,19 +1408,19 @@
         <v>5</v>
       </c>
       <c r="F15" s="3">
-        <v>61100</v>
+        <v>61400</v>
       </c>
       <c r="G15" s="3">
-        <v>59200</v>
+        <v>59400</v>
       </c>
       <c r="H15" s="3">
-        <v>61900</v>
+        <v>62200</v>
       </c>
       <c r="I15" s="3">
-        <v>55600</v>
+        <v>55800</v>
       </c>
       <c r="J15" s="3">
-        <v>53200</v>
+        <v>53400</v>
       </c>
       <c r="K15" s="3">
         <v>53300</v>
@@ -1529,25 +1529,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>252800</v>
+        <v>253700</v>
       </c>
       <c r="E17" s="3">
-        <v>198000</v>
+        <v>198700</v>
       </c>
       <c r="F17" s="3">
-        <v>213700</v>
+        <v>214500</v>
       </c>
       <c r="G17" s="3">
-        <v>222800</v>
+        <v>223600</v>
       </c>
       <c r="H17" s="3">
-        <v>217100</v>
+        <v>217800</v>
       </c>
       <c r="I17" s="3">
-        <v>187500</v>
+        <v>188100</v>
       </c>
       <c r="J17" s="3">
-        <v>228600</v>
+        <v>229400</v>
       </c>
       <c r="K17" s="3">
         <v>216700</v>
@@ -1624,7 +1624,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>35100</v>
+        <v>35200</v>
       </c>
       <c r="E18" s="3">
         <v>2300</v>
@@ -1642,7 +1642,7 @@
         <v>-4300</v>
       </c>
       <c r="J18" s="3">
-        <v>-77500</v>
+        <v>-77800</v>
       </c>
       <c r="K18" s="3">
         <v>-27100</v>
@@ -1757,22 +1757,22 @@
         <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>-44100</v>
+        <v>-44300</v>
       </c>
       <c r="F20" s="3">
         <v>11400</v>
       </c>
       <c r="G20" s="3">
-        <v>10100</v>
+        <v>10200</v>
       </c>
       <c r="H20" s="3">
-        <v>25800</v>
+        <v>25900</v>
       </c>
       <c r="I20" s="3">
-        <v>-30400</v>
+        <v>-30500</v>
       </c>
       <c r="J20" s="3">
-        <v>-29800</v>
+        <v>-29900</v>
       </c>
       <c r="K20" s="3">
         <v>-10500</v>
@@ -1849,25 +1849,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>39400</v>
+        <v>39600</v>
       </c>
       <c r="E21" s="3">
-        <v>23100</v>
+        <v>23200</v>
       </c>
       <c r="F21" s="3">
-        <v>72100</v>
+        <v>72400</v>
       </c>
       <c r="G21" s="3">
-        <v>63200</v>
+        <v>63500</v>
       </c>
       <c r="H21" s="3">
-        <v>84200</v>
+        <v>84500</v>
       </c>
       <c r="I21" s="3">
-        <v>21000</v>
+        <v>21100</v>
       </c>
       <c r="J21" s="3">
-        <v>-54100</v>
+        <v>-54300</v>
       </c>
       <c r="K21" s="3">
         <v>15700</v>
@@ -1953,10 +1953,10 @@
         <v>13300</v>
       </c>
       <c r="G22" s="3">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="H22" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="I22" s="3">
         <v>9200</v>
@@ -2039,25 +2039,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>34700</v>
+        <v>34800</v>
       </c>
       <c r="E23" s="3">
-        <v>-41800</v>
+        <v>-42000</v>
       </c>
       <c r="F23" s="3">
         <v>-2300</v>
       </c>
       <c r="G23" s="3">
-        <v>-7200</v>
+        <v>-7300</v>
       </c>
       <c r="H23" s="3">
         <v>11800</v>
       </c>
       <c r="I23" s="3">
-        <v>-43800</v>
+        <v>-44000</v>
       </c>
       <c r="J23" s="3">
-        <v>-117100</v>
+        <v>-117500</v>
       </c>
       <c r="K23" s="3">
         <v>-44500</v>
@@ -2134,7 +2134,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="E24" s="3">
         <v>-9000</v>
@@ -2149,10 +2149,10 @@
         <v>3800</v>
       </c>
       <c r="I24" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="J24" s="3">
-        <v>-26800</v>
+        <v>-26900</v>
       </c>
       <c r="K24" s="3">
         <v>-10200</v>
@@ -2324,10 +2324,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E26" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="F26" s="3">
         <v>-3700</v>
@@ -2336,13 +2336,13 @@
         <v>-7100</v>
       </c>
       <c r="H26" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I26" s="3">
-        <v>-33800</v>
+        <v>-33900</v>
       </c>
       <c r="J26" s="3">
-        <v>-90300</v>
+        <v>-90700</v>
       </c>
       <c r="K26" s="3">
         <v>-34400</v>
@@ -2419,10 +2419,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E27" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="F27" s="3">
         <v>-3700</v>
@@ -2431,13 +2431,13 @@
         <v>-7100</v>
       </c>
       <c r="H27" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I27" s="3">
-        <v>-33800</v>
+        <v>-33900</v>
       </c>
       <c r="J27" s="3">
-        <v>-90300</v>
+        <v>-90700</v>
       </c>
       <c r="K27" s="3">
         <v>-34400</v>
@@ -2897,22 +2897,22 @@
         <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>44100</v>
+        <v>44300</v>
       </c>
       <c r="F32" s="3">
         <v>-11400</v>
       </c>
       <c r="G32" s="3">
-        <v>-10100</v>
+        <v>-10200</v>
       </c>
       <c r="H32" s="3">
-        <v>-25800</v>
+        <v>-25900</v>
       </c>
       <c r="I32" s="3">
-        <v>30400</v>
+        <v>30500</v>
       </c>
       <c r="J32" s="3">
-        <v>29800</v>
+        <v>29900</v>
       </c>
       <c r="K32" s="3">
         <v>10500</v>
@@ -2989,10 +2989,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E33" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="F33" s="3">
         <v>-3700</v>
@@ -3001,13 +3001,13 @@
         <v>-7100</v>
       </c>
       <c r="H33" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I33" s="3">
-        <v>-33800</v>
+        <v>-33900</v>
       </c>
       <c r="J33" s="3">
-        <v>-90300</v>
+        <v>-90700</v>
       </c>
       <c r="K33" s="3">
         <v>-34400</v>
@@ -3179,10 +3179,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E35" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="F35" s="3">
         <v>-3700</v>
@@ -3191,13 +3191,13 @@
         <v>-7100</v>
       </c>
       <c r="H35" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I35" s="3">
-        <v>-33800</v>
+        <v>-33900</v>
       </c>
       <c r="J35" s="3">
-        <v>-90300</v>
+        <v>-90700</v>
       </c>
       <c r="K35" s="3">
         <v>-34400</v>
@@ -3444,25 +3444,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>80100</v>
+        <v>80400</v>
       </c>
       <c r="E41" s="3">
-        <v>103100</v>
+        <v>103400</v>
       </c>
       <c r="F41" s="3">
-        <v>96900</v>
+        <v>97300</v>
       </c>
       <c r="G41" s="3">
-        <v>94000</v>
+        <v>94300</v>
       </c>
       <c r="H41" s="3">
-        <v>39600</v>
+        <v>39700</v>
       </c>
       <c r="I41" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="J41" s="3">
-        <v>154600</v>
+        <v>155100</v>
       </c>
       <c r="K41" s="3">
         <v>118800</v>
@@ -3634,25 +3634,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>185200</v>
+        <v>185900</v>
       </c>
       <c r="E43" s="3">
-        <v>112100</v>
+        <v>112500</v>
       </c>
       <c r="F43" s="3">
-        <v>114400</v>
+        <v>114800</v>
       </c>
       <c r="G43" s="3">
-        <v>165300</v>
+        <v>165900</v>
       </c>
       <c r="H43" s="3">
-        <v>225500</v>
+        <v>226300</v>
       </c>
       <c r="I43" s="3">
-        <v>132400</v>
+        <v>132900</v>
       </c>
       <c r="J43" s="3">
-        <v>116800</v>
+        <v>117200</v>
       </c>
       <c r="K43" s="3">
         <v>129200</v>
@@ -3732,7 +3732,7 @@
         <v>5100</v>
       </c>
       <c r="E44" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="F44" s="3">
         <v>4000</v>
@@ -3824,25 +3824,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37500</v>
+        <v>37600</v>
       </c>
       <c r="E45" s="3">
-        <v>54900</v>
+        <v>55100</v>
       </c>
       <c r="F45" s="3">
-        <v>31600</v>
+        <v>31700</v>
       </c>
       <c r="G45" s="3">
-        <v>28700</v>
+        <v>28800</v>
       </c>
       <c r="H45" s="3">
-        <v>43300</v>
+        <v>43500</v>
       </c>
       <c r="I45" s="3">
-        <v>54900</v>
+        <v>55100</v>
       </c>
       <c r="J45" s="3">
-        <v>28200</v>
+        <v>28300</v>
       </c>
       <c r="K45" s="3">
         <v>27000</v>
@@ -3919,25 +3919,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>307900</v>
+        <v>309000</v>
       </c>
       <c r="E46" s="3">
-        <v>276500</v>
+        <v>277500</v>
       </c>
       <c r="F46" s="3">
-        <v>247000</v>
+        <v>247900</v>
       </c>
       <c r="G46" s="3">
-        <v>291400</v>
+        <v>292400</v>
       </c>
       <c r="H46" s="3">
-        <v>312500</v>
+        <v>313600</v>
       </c>
       <c r="I46" s="3">
-        <v>223000</v>
+        <v>223800</v>
       </c>
       <c r="J46" s="3">
-        <v>302400</v>
+        <v>303500</v>
       </c>
       <c r="K46" s="3">
         <v>278400</v>
@@ -4014,25 +4014,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>31200</v>
+        <v>31300</v>
       </c>
       <c r="E47" s="3">
-        <v>57400</v>
+        <v>57600</v>
       </c>
       <c r="F47" s="3">
-        <v>28400</v>
+        <v>28500</v>
       </c>
       <c r="G47" s="3">
-        <v>27400</v>
+        <v>27500</v>
       </c>
       <c r="H47" s="3">
-        <v>27100</v>
+        <v>27200</v>
       </c>
       <c r="I47" s="3">
-        <v>24600</v>
+        <v>24700</v>
       </c>
       <c r="J47" s="3">
-        <v>37900</v>
+        <v>38100</v>
       </c>
       <c r="K47" s="3">
         <v>43900</v>
@@ -4109,25 +4109,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>361200</v>
+        <v>362500</v>
       </c>
       <c r="E48" s="3">
-        <v>363800</v>
+        <v>365100</v>
       </c>
       <c r="F48" s="3">
-        <v>359600</v>
+        <v>360900</v>
       </c>
       <c r="G48" s="3">
-        <v>338900</v>
+        <v>340000</v>
       </c>
       <c r="H48" s="3">
-        <v>340300</v>
+        <v>341600</v>
       </c>
       <c r="I48" s="3">
-        <v>342400</v>
+        <v>343600</v>
       </c>
       <c r="J48" s="3">
-        <v>340500</v>
+        <v>341700</v>
       </c>
       <c r="K48" s="3">
         <v>333200</v>
@@ -4204,25 +4204,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1176300</v>
+        <v>1180500</v>
       </c>
       <c r="E49" s="3">
-        <v>1232700</v>
+        <v>1237100</v>
       </c>
       <c r="F49" s="3">
-        <v>1035900</v>
+        <v>1039500</v>
       </c>
       <c r="G49" s="3">
-        <v>1075300</v>
+        <v>1079100</v>
       </c>
       <c r="H49" s="3">
-        <v>1111300</v>
+        <v>1115200</v>
       </c>
       <c r="I49" s="3">
-        <v>1174300</v>
+        <v>1178400</v>
       </c>
       <c r="J49" s="3">
-        <v>947800</v>
+        <v>951100</v>
       </c>
       <c r="K49" s="3">
         <v>963400</v>
@@ -4501,13 +4501,13 @@
         <v>19300</v>
       </c>
       <c r="H52" s="3">
-        <v>28300</v>
+        <v>28400</v>
       </c>
       <c r="I52" s="3">
-        <v>47600</v>
+        <v>47800</v>
       </c>
       <c r="J52" s="3">
-        <v>21000</v>
+        <v>21100</v>
       </c>
       <c r="K52" s="3">
         <v>8700</v>
@@ -4679,25 +4679,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1877000</v>
+        <v>1883600</v>
       </c>
       <c r="E54" s="3">
-        <v>1938700</v>
+        <v>1945500</v>
       </c>
       <c r="F54" s="3">
-        <v>1680500</v>
+        <v>1686500</v>
       </c>
       <c r="G54" s="3">
-        <v>1752200</v>
+        <v>1758400</v>
       </c>
       <c r="H54" s="3">
-        <v>1819500</v>
+        <v>1826000</v>
       </c>
       <c r="I54" s="3">
-        <v>1812000</v>
+        <v>1818400</v>
       </c>
       <c r="J54" s="3">
-        <v>1649600</v>
+        <v>1655400</v>
       </c>
       <c r="K54" s="3">
         <v>1627600</v>
@@ -4844,25 +4844,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>295400</v>
+        <v>296500</v>
       </c>
       <c r="E57" s="3">
-        <v>341400</v>
+        <v>342600</v>
       </c>
       <c r="F57" s="3">
-        <v>301500</v>
+        <v>302600</v>
       </c>
       <c r="G57" s="3">
-        <v>300300</v>
+        <v>301400</v>
       </c>
       <c r="H57" s="3">
-        <v>290400</v>
+        <v>291500</v>
       </c>
       <c r="I57" s="3">
-        <v>329500</v>
+        <v>330700</v>
       </c>
       <c r="J57" s="3">
-        <v>281300</v>
+        <v>282300</v>
       </c>
       <c r="K57" s="3">
         <v>268200</v>
@@ -4939,25 +4939,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>341300</v>
+        <v>342500</v>
       </c>
       <c r="E58" s="3">
-        <v>261800</v>
+        <v>262800</v>
       </c>
       <c r="F58" s="3">
-        <v>136400</v>
+        <v>136900</v>
       </c>
       <c r="G58" s="3">
-        <v>260700</v>
+        <v>261600</v>
       </c>
       <c r="H58" s="3">
-        <v>264000</v>
+        <v>264900</v>
       </c>
       <c r="I58" s="3">
-        <v>132500</v>
+        <v>132900</v>
       </c>
       <c r="J58" s="3">
-        <v>136800</v>
+        <v>137300</v>
       </c>
       <c r="K58" s="3">
         <v>128900</v>
@@ -5034,25 +5034,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>206700</v>
+        <v>207400</v>
       </c>
       <c r="E59" s="3">
-        <v>288400</v>
+        <v>289400</v>
       </c>
       <c r="F59" s="3">
-        <v>233900</v>
+        <v>234700</v>
       </c>
       <c r="G59" s="3">
-        <v>182000</v>
+        <v>182700</v>
       </c>
       <c r="H59" s="3">
-        <v>221200</v>
+        <v>222000</v>
       </c>
       <c r="I59" s="3">
-        <v>219900</v>
+        <v>220700</v>
       </c>
       <c r="J59" s="3">
-        <v>212900</v>
+        <v>213600</v>
       </c>
       <c r="K59" s="3">
         <v>178500</v>
@@ -5129,25 +5129,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>843400</v>
+        <v>846400</v>
       </c>
       <c r="E60" s="3">
-        <v>891600</v>
+        <v>894800</v>
       </c>
       <c r="F60" s="3">
-        <v>671800</v>
+        <v>674200</v>
       </c>
       <c r="G60" s="3">
-        <v>743000</v>
+        <v>745600</v>
       </c>
       <c r="H60" s="3">
-        <v>775600</v>
+        <v>778400</v>
       </c>
       <c r="I60" s="3">
-        <v>681900</v>
+        <v>684300</v>
       </c>
       <c r="J60" s="3">
-        <v>631000</v>
+        <v>633200</v>
       </c>
       <c r="K60" s="3">
         <v>575700</v>
@@ -5224,25 +5224,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>655700</v>
+        <v>658000</v>
       </c>
       <c r="E61" s="3">
-        <v>684200</v>
+        <v>686600</v>
       </c>
       <c r="F61" s="3">
-        <v>656900</v>
+        <v>659200</v>
       </c>
       <c r="G61" s="3">
-        <v>668000</v>
+        <v>670300</v>
       </c>
       <c r="H61" s="3">
-        <v>686200</v>
+        <v>688600</v>
       </c>
       <c r="I61" s="3">
-        <v>739500</v>
+        <v>742100</v>
       </c>
       <c r="J61" s="3">
-        <v>679900</v>
+        <v>682300</v>
       </c>
       <c r="K61" s="3">
         <v>610600</v>
@@ -5319,25 +5319,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>255500</v>
+        <v>256400</v>
       </c>
       <c r="E62" s="3">
-        <v>271100</v>
+        <v>272100</v>
       </c>
       <c r="F62" s="3">
-        <v>219200</v>
+        <v>220000</v>
       </c>
       <c r="G62" s="3">
-        <v>207900</v>
+        <v>208700</v>
       </c>
       <c r="H62" s="3">
-        <v>217800</v>
+        <v>218500</v>
       </c>
       <c r="I62" s="3">
-        <v>261500</v>
+        <v>262400</v>
       </c>
       <c r="J62" s="3">
-        <v>176100</v>
+        <v>176700</v>
       </c>
       <c r="K62" s="3">
         <v>178900</v>
@@ -5699,25 +5699,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1754500</v>
+        <v>1760700</v>
       </c>
       <c r="E66" s="3">
-        <v>1846900</v>
+        <v>1853400</v>
       </c>
       <c r="F66" s="3">
-        <v>1548000</v>
+        <v>1553400</v>
       </c>
       <c r="G66" s="3">
-        <v>1618900</v>
+        <v>1624600</v>
       </c>
       <c r="H66" s="3">
-        <v>1679600</v>
+        <v>1685500</v>
       </c>
       <c r="I66" s="3">
-        <v>1682900</v>
+        <v>1688800</v>
       </c>
       <c r="J66" s="3">
-        <v>1487000</v>
+        <v>1492200</v>
       </c>
       <c r="K66" s="3">
         <v>1365200</v>
@@ -6209,25 +6209,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>61800</v>
+        <v>62000</v>
       </c>
       <c r="E72" s="3">
-        <v>34900</v>
+        <v>35000</v>
       </c>
       <c r="F72" s="3">
-        <v>66800</v>
+        <v>67000</v>
       </c>
       <c r="G72" s="3">
-        <v>70100</v>
+        <v>70300</v>
       </c>
       <c r="H72" s="3">
-        <v>76400</v>
+        <v>76700</v>
       </c>
       <c r="I72" s="3">
-        <v>67600</v>
+        <v>67800</v>
       </c>
       <c r="J72" s="3">
-        <v>100700</v>
+        <v>101100</v>
       </c>
       <c r="K72" s="3">
         <v>202400</v>
@@ -6589,25 +6589,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>122400</v>
+        <v>122900</v>
       </c>
       <c r="E76" s="3">
-        <v>91800</v>
+        <v>92100</v>
       </c>
       <c r="F76" s="3">
-        <v>132500</v>
+        <v>133000</v>
       </c>
       <c r="G76" s="3">
-        <v>133300</v>
+        <v>133700</v>
       </c>
       <c r="H76" s="3">
-        <v>139900</v>
+        <v>140400</v>
       </c>
       <c r="I76" s="3">
-        <v>129100</v>
+        <v>129500</v>
       </c>
       <c r="J76" s="3">
-        <v>162600</v>
+        <v>163200</v>
       </c>
       <c r="K76" s="3">
         <v>262400</v>
@@ -6879,10 +6879,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="E81" s="3">
-        <v>-32800</v>
+        <v>-33000</v>
       </c>
       <c r="F81" s="3">
         <v>-3700</v>
@@ -6891,13 +6891,13 @@
         <v>-7100</v>
       </c>
       <c r="H81" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="I81" s="3">
-        <v>-33800</v>
+        <v>-33900</v>
       </c>
       <c r="J81" s="3">
-        <v>-90300</v>
+        <v>-90700</v>
       </c>
       <c r="K81" s="3">
         <v>-34400</v>
@@ -7015,19 +7015,19 @@
         <v>5</v>
       </c>
       <c r="F83" s="3">
-        <v>61100</v>
+        <v>61400</v>
       </c>
       <c r="G83" s="3">
-        <v>59200</v>
+        <v>59400</v>
       </c>
       <c r="H83" s="3">
-        <v>61900</v>
+        <v>62200</v>
       </c>
       <c r="I83" s="3">
-        <v>55600</v>
+        <v>55800</v>
       </c>
       <c r="J83" s="3">
-        <v>53200</v>
+        <v>53400</v>
       </c>
       <c r="K83" s="3">
         <v>53300</v>
@@ -7579,25 +7579,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-59300</v>
+        <v>-59500</v>
       </c>
       <c r="E89" s="3">
-        <v>27400</v>
+        <v>27500</v>
       </c>
       <c r="F89" s="3">
-        <v>139300</v>
+        <v>139800</v>
       </c>
       <c r="G89" s="3">
-        <v>68900</v>
+        <v>69200</v>
       </c>
       <c r="H89" s="3">
-        <v>-78400</v>
+        <v>-78700</v>
       </c>
       <c r="I89" s="3">
         <v>-7700</v>
       </c>
       <c r="J89" s="3">
-        <v>52400</v>
+        <v>52600</v>
       </c>
       <c r="K89" s="3">
         <v>28800</v>
@@ -7994,10 +7994,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-39100</v>
+        <v>-39200</v>
       </c>
       <c r="E94" s="3">
-        <v>-147400</v>
+        <v>-147900</v>
       </c>
       <c r="F94" s="3">
         <v>-7000</v>
@@ -8006,10 +8006,10 @@
         <v>-14600</v>
       </c>
       <c r="H94" s="3">
-        <v>-38900</v>
+        <v>-39000</v>
       </c>
       <c r="I94" s="3">
-        <v>-118300</v>
+        <v>-118700</v>
       </c>
       <c r="J94" s="3">
         <v>-7800</v>
@@ -8504,25 +8504,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>76100</v>
+        <v>76400</v>
       </c>
       <c r="E100" s="3">
-        <v>127300</v>
+        <v>127700</v>
       </c>
       <c r="F100" s="3">
-        <v>-128000</v>
+        <v>-128400</v>
       </c>
       <c r="G100" s="3">
         <v>-200</v>
       </c>
       <c r="H100" s="3">
-        <v>126800</v>
+        <v>127200</v>
       </c>
       <c r="I100" s="3">
         <v>-1100</v>
       </c>
       <c r="J100" s="3">
-        <v>-15400</v>
+        <v>-15500</v>
       </c>
       <c r="K100" s="3">
         <v>-14100</v>
@@ -8617,7 +8617,7 @@
         <v>3500</v>
       </c>
       <c r="J101" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="K101" s="3">
         <v>500</v>
@@ -8694,25 +8694,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-23000</v>
+        <v>-23100</v>
       </c>
       <c r="E102" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="F102" s="3">
         <v>2900</v>
       </c>
       <c r="G102" s="3">
-        <v>54400</v>
+        <v>54600</v>
       </c>
       <c r="H102" s="3">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="I102" s="3">
-        <v>-123600</v>
+        <v>-124100</v>
       </c>
       <c r="J102" s="3">
-        <v>32400</v>
+        <v>32500</v>
       </c>
       <c r="K102" s="3">
         <v>10400</v>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,238 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>288900</v>
+        <v>186600</v>
       </c>
       <c r="E8" s="3">
-        <v>201000</v>
+        <v>179400</v>
       </c>
       <c r="F8" s="3">
-        <v>214100</v>
+        <v>296300</v>
       </c>
       <c r="G8" s="3">
-        <v>217500</v>
+        <v>206100</v>
       </c>
       <c r="H8" s="3">
-        <v>214200</v>
+        <v>219500</v>
       </c>
       <c r="I8" s="3">
+        <v>223100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>219700</v>
+      </c>
+      <c r="K8" s="3">
         <v>183900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>151600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>189600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>230000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>160300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>116600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>141100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>202500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>128900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>99400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>164700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>229800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>184700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>185900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>202500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>275500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>178300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>157200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>190200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>231400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>187400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>229400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>167500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>207900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +995,14 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,19 +1335,25 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="E14" s="3">
+        <v>39800</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
@@ -1325,174 +1365,186 @@
         <v>5</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>18800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>12400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>4600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>1600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>25900</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2500</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
+      <c r="E15" s="3">
+        <v>66100</v>
       </c>
       <c r="F15" s="3">
-        <v>61400</v>
+        <v>71700</v>
       </c>
       <c r="G15" s="3">
-        <v>59400</v>
+        <v>66900</v>
       </c>
       <c r="H15" s="3">
-        <v>62200</v>
+        <v>62900</v>
       </c>
       <c r="I15" s="3">
+        <v>60900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>63700</v>
+      </c>
+      <c r="K15" s="3">
         <v>55800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>53400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>53300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>52400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>49200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>41400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>41200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>42300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>41800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>42400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>48000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>47600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>48900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>47000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>44300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>48100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>50100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>45800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>45300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>52300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>50400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>41500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>42900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>48800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>253700</v>
+        <v>229100</v>
       </c>
       <c r="E17" s="3">
-        <v>198700</v>
+        <v>266300</v>
       </c>
       <c r="F17" s="3">
-        <v>214500</v>
+        <v>260200</v>
       </c>
       <c r="G17" s="3">
-        <v>223600</v>
+        <v>203800</v>
       </c>
       <c r="H17" s="3">
-        <v>217800</v>
+        <v>219900</v>
       </c>
       <c r="I17" s="3">
+        <v>229300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>223400</v>
+      </c>
+      <c r="K17" s="3">
         <v>188100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>229400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>216700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>223400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>173100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>162200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>166800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>145700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>161000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>146900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>169100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>180000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>169700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>217300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>183500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>217400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>160000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>187500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>180800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>176400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>164000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>175800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>172900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>158300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>35200</v>
+        <v>-42500</v>
       </c>
       <c r="E18" s="3">
-        <v>2300</v>
+        <v>-86900</v>
       </c>
       <c r="F18" s="3">
+        <v>36100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3600</v>
-      </c>
       <c r="I18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-77800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-27100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-12800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-45600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-25700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>56800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-32000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-47500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>49800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-31400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>19000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>58100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>18300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>9400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>55000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>23400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>53600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>49600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1814,515 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>-12000</v>
       </c>
       <c r="E20" s="3">
-        <v>-44300</v>
+        <v>-9600</v>
       </c>
       <c r="F20" s="3">
-        <v>11400</v>
+        <v>14200</v>
       </c>
       <c r="G20" s="3">
-        <v>10200</v>
+        <v>-33500</v>
       </c>
       <c r="H20" s="3">
-        <v>25900</v>
+        <v>11700</v>
       </c>
       <c r="I20" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>26600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-30500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-29900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-10500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-5600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>28800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-26700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>27300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>7000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>5600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>39600</v>
+        <v>-192800</v>
       </c>
       <c r="E21" s="3">
-        <v>23200</v>
+        <v>-30400</v>
       </c>
       <c r="F21" s="3">
-        <v>72400</v>
+        <v>122000</v>
       </c>
       <c r="G21" s="3">
-        <v>63500</v>
+        <v>35700</v>
       </c>
       <c r="H21" s="3">
-        <v>84500</v>
+        <v>74200</v>
       </c>
       <c r="I21" s="3">
+        <v>65100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>86600</v>
+      </c>
+      <c r="K21" s="3">
         <v>21100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-54300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>15700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>56400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>30800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>19900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>128000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>16900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>124600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>60000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>12000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>65400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>104800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>68200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>61600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>108000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>79400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>98100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>39700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>89700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
+      <c r="E22" s="3">
+        <v>13100</v>
       </c>
       <c r="F22" s="3">
-        <v>13300</v>
+        <v>14600</v>
       </c>
       <c r="G22" s="3">
-        <v>11400</v>
+        <v>11900</v>
       </c>
       <c r="H22" s="3">
-        <v>10500</v>
+        <v>13700</v>
       </c>
       <c r="I22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K22" s="3">
         <v>9200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>9800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>6900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>6600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>6700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>6700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>6100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>5800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>6900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>6500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>7700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>7000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>6500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>5600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>6400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>6700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>7000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>6500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>7100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>34800</v>
+        <v>-54500</v>
       </c>
       <c r="E23" s="3">
-        <v>-42000</v>
+        <v>-109700</v>
       </c>
       <c r="F23" s="3">
+        <v>35700</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>11800</v>
-      </c>
       <c r="I23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-44000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-117500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-44500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-52200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-27500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>79800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-32000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-56800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-38000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>70600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-42500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>14800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>49700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>11600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>10700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>49300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>22300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>49600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>33800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>8800</v>
+        <v>-6900</v>
       </c>
       <c r="E24" s="3">
-        <v>-9000</v>
+        <v>-15800</v>
       </c>
       <c r="F24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K24" s="3">
         <v>-10100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-26900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-10200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-5400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-8500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-11300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-13700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>17400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-11100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>4600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>14400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>11100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>9900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>10700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>26100</v>
+        <v>-47600</v>
       </c>
       <c r="E26" s="3">
-        <v>-33000</v>
+        <v>-93800</v>
       </c>
       <c r="F26" s="3">
-        <v>-3700</v>
+        <v>26700</v>
       </c>
       <c r="G26" s="3">
-        <v>-7100</v>
+        <v>-33800</v>
       </c>
       <c r="H26" s="3">
-        <v>8100</v>
+        <v>-3800</v>
       </c>
       <c r="I26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-33900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-90700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-34400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-19700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-53700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-18900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>84000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-31900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-45500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-24300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>53200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-31400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>10200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>35400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>8800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>8900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>38200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>12500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>31600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>23100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>26100</v>
+        <v>-47600</v>
       </c>
       <c r="E27" s="3">
-        <v>-33000</v>
+        <v>-93800</v>
       </c>
       <c r="F27" s="3">
-        <v>-3700</v>
+        <v>26700</v>
       </c>
       <c r="G27" s="3">
-        <v>-7100</v>
+        <v>-33800</v>
       </c>
       <c r="H27" s="3">
-        <v>8100</v>
+        <v>-3800</v>
       </c>
       <c r="I27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-33900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-90700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-34400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-19700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-53700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-18900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>84000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-31900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-45500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-24300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>53200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-31400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>10200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>35400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>8800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>8900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>38200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>12500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>31600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>23100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2614,23 +2736,23 @@
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2639,56 +2761,56 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-79900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-2700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-3900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>1000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-6200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-5400</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2820,14 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>12000</v>
       </c>
       <c r="E32" s="3">
-        <v>44300</v>
+        <v>9600</v>
       </c>
       <c r="F32" s="3">
-        <v>-11400</v>
+        <v>-14200</v>
       </c>
       <c r="G32" s="3">
-        <v>-10200</v>
+        <v>33500</v>
       </c>
       <c r="H32" s="3">
-        <v>-25900</v>
+        <v>-11700</v>
       </c>
       <c r="I32" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="K32" s="3">
         <v>30500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>29900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>10500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>5600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-28800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>26700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-27300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>11200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>8700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>26100</v>
+        <v>-47600</v>
       </c>
       <c r="E33" s="3">
-        <v>-33000</v>
+        <v>-93800</v>
       </c>
       <c r="F33" s="3">
-        <v>-3700</v>
+        <v>26700</v>
       </c>
       <c r="G33" s="3">
-        <v>-7100</v>
+        <v>-33800</v>
       </c>
       <c r="H33" s="3">
-        <v>8100</v>
+        <v>-3800</v>
       </c>
       <c r="I33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-33900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-90700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-34400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-19700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-133600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-21600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>74800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-35800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-44500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-30400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>47700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-31400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>10200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>35400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>8800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>8900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>12500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>31600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>23100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>26100</v>
+        <v>-47600</v>
       </c>
       <c r="E35" s="3">
-        <v>-33000</v>
+        <v>-93800</v>
       </c>
       <c r="F35" s="3">
-        <v>-3700</v>
+        <v>26700</v>
       </c>
       <c r="G35" s="3">
-        <v>-7100</v>
+        <v>-33800</v>
       </c>
       <c r="H35" s="3">
-        <v>8100</v>
+        <v>-3800</v>
       </c>
       <c r="I35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-33900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-90700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-34400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-19700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-133600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-21600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>74800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-35800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-44500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-30400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>47700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-31400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>10200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>35400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>8800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>8900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>12500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>31600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>23100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3610,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>80400</v>
+        <v>96500</v>
       </c>
       <c r="E41" s="3">
-        <v>103400</v>
+        <v>87900</v>
       </c>
       <c r="F41" s="3">
-        <v>97300</v>
+        <v>82400</v>
       </c>
       <c r="G41" s="3">
-        <v>94300</v>
+        <v>106100</v>
       </c>
       <c r="H41" s="3">
-        <v>39700</v>
+        <v>99800</v>
       </c>
       <c r="I41" s="3">
+        <v>96800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>40700</v>
+      </c>
+      <c r="K41" s="3">
         <v>31100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>155100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>118800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>108500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>125000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>137300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>101000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>94400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>69700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>62900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>120100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>137500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>191300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>435300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>258100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>251500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>326900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>312900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>209100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>202600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>282000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>378600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>201000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>161600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,673 +3808,721 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>185900</v>
+        <v>104300</v>
       </c>
       <c r="E43" s="3">
-        <v>112500</v>
+        <v>122600</v>
       </c>
       <c r="F43" s="3">
+        <v>190600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>115400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>117800</v>
+      </c>
+      <c r="I43" s="3">
+        <v>170100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>232000</v>
+      </c>
+      <c r="K43" s="3">
+        <v>132900</v>
+      </c>
+      <c r="L43" s="3">
+        <v>117200</v>
+      </c>
+      <c r="M43" s="3">
+        <v>129200</v>
+      </c>
+      <c r="N43" s="3">
+        <v>156100</v>
+      </c>
+      <c r="O43" s="3">
+        <v>107000</v>
+      </c>
+      <c r="P43" s="3">
         <v>114800</v>
       </c>
-      <c r="G43" s="3">
-        <v>165900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>226300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>132900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>117200</v>
-      </c>
-      <c r="K43" s="3">
-        <v>129200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>156100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>107000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>114800</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>101500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>152600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>116300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>199300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>113300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>144100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>125300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>92300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>247800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>164900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>122400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>218300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>152200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>160500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>111200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>135300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>114100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>163800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5100</v>
+        <v>4600</v>
       </c>
       <c r="E44" s="3">
-        <v>6500</v>
+        <v>4900</v>
       </c>
       <c r="F44" s="3">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="G44" s="3">
-        <v>3400</v>
+        <v>6600</v>
       </c>
       <c r="H44" s="3">
         <v>4200</v>
       </c>
       <c r="I44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K44" s="3">
         <v>4800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>3400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>2500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>2700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>2100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37600</v>
+        <v>27100</v>
       </c>
       <c r="E45" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F45" s="3">
+        <v>38600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>56500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>32500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>29500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>44600</v>
+      </c>
+      <c r="K45" s="3">
         <v>55100</v>
       </c>
-      <c r="F45" s="3">
-        <v>31700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>28800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>43500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>55100</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>28300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>27300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>34300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>9600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>21000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>25700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>9400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>15400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>18000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>21400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>18900</v>
-      </c>
-      <c r="W45" s="3">
-        <v>700</v>
-      </c>
-      <c r="X45" s="3">
-        <v>800</v>
       </c>
       <c r="Y45" s="3">
         <v>700</v>
       </c>
       <c r="Z45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB45" s="3">
         <v>1500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>3200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>4200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>5200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>6000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>309000</v>
+        <v>232600</v>
       </c>
       <c r="E46" s="3">
-        <v>277500</v>
+        <v>240000</v>
       </c>
       <c r="F46" s="3">
-        <v>247900</v>
+        <v>316900</v>
       </c>
       <c r="G46" s="3">
-        <v>292400</v>
+        <v>284600</v>
       </c>
       <c r="H46" s="3">
-        <v>313600</v>
+        <v>254200</v>
       </c>
       <c r="I46" s="3">
+        <v>299800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>321600</v>
+      </c>
+      <c r="K46" s="3">
         <v>223800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>303500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>278400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>295400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>269900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>264200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>221400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>271400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>215800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>274200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>252100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>303100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>341700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>549500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>509300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>420600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>453500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>534500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>366700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>369100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>399100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>520200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>322100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>332900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>31300</v>
+        <v>36600</v>
       </c>
       <c r="E47" s="3">
-        <v>57600</v>
+        <v>32400</v>
       </c>
       <c r="F47" s="3">
-        <v>28500</v>
+        <v>32100</v>
       </c>
       <c r="G47" s="3">
-        <v>27500</v>
+        <v>59100</v>
       </c>
       <c r="H47" s="3">
-        <v>27200</v>
+        <v>29300</v>
       </c>
       <c r="I47" s="3">
+        <v>28200</v>
+      </c>
+      <c r="J47" s="3">
+        <v>27900</v>
+      </c>
+      <c r="K47" s="3">
         <v>24700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>38100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>43900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>50900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>54200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>25300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>31500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>40200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>29700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>53300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>56500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>55400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>57100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>14000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>14000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>14400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>14100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>6800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>8600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>16200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>13000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>20100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>19700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>5600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>362500</v>
+        <v>372700</v>
       </c>
       <c r="E48" s="3">
-        <v>365100</v>
+        <v>370800</v>
       </c>
       <c r="F48" s="3">
-        <v>360900</v>
+        <v>371700</v>
       </c>
       <c r="G48" s="3">
-        <v>340000</v>
+        <v>374400</v>
       </c>
       <c r="H48" s="3">
-        <v>341600</v>
+        <v>370100</v>
       </c>
       <c r="I48" s="3">
+        <v>348700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>350300</v>
+      </c>
+      <c r="K48" s="3">
         <v>343600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>341700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>333200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>335000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>344400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>337500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>327100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>323100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>328800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>341400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>378900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>386600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>384000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>383500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>346300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>344300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>345200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>353000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>352800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>661600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>340100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>337400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>339900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>339900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1180500</v>
+        <v>1099100</v>
       </c>
       <c r="E49" s="3">
-        <v>1237100</v>
+        <v>1151200</v>
       </c>
       <c r="F49" s="3">
-        <v>1039500</v>
+        <v>1210500</v>
       </c>
       <c r="G49" s="3">
-        <v>1079100</v>
+        <v>1268600</v>
       </c>
       <c r="H49" s="3">
-        <v>1115200</v>
+        <v>1066000</v>
       </c>
       <c r="I49" s="3">
+        <v>1106600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1143600</v>
+      </c>
+      <c r="K49" s="3">
         <v>1178400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>951100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>963400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1007700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1075800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>936100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>926100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>910700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>923400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>945600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1044600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1034400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1071500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1088000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>956700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>976700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1013600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>972200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>935900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>931700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3">
-        <v>8200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>9600</v>
-      </c>
       <c r="G52" s="3">
-        <v>19300</v>
+        <v>8400</v>
       </c>
       <c r="H52" s="3">
-        <v>28400</v>
+        <v>9800</v>
       </c>
       <c r="I52" s="3">
+        <v>19800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K52" s="3">
         <v>47800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>21100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>8700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>74600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>73000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>65500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>73200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>73500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>73500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>75800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>82700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>77000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>79500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>88400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>88100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>104000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>102600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>177500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>186700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>192900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>194100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1883600</v>
+        <v>1764600</v>
       </c>
       <c r="E54" s="3">
-        <v>1945500</v>
+        <v>1809800</v>
       </c>
       <c r="F54" s="3">
-        <v>1686500</v>
+        <v>1931600</v>
       </c>
       <c r="G54" s="3">
-        <v>1758400</v>
+        <v>1995100</v>
       </c>
       <c r="H54" s="3">
-        <v>1826000</v>
+        <v>1729400</v>
       </c>
       <c r="I54" s="3">
+        <v>1803100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1872500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1818400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1655400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1627600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1694500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1750700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1563800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1580700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1618300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1563300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1687700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1805500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1852900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1930100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2117700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1903300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1835600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1914900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +5098,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>296500</v>
+        <v>326800</v>
       </c>
       <c r="E57" s="3">
-        <v>342600</v>
+        <v>286100</v>
       </c>
       <c r="F57" s="3">
-        <v>302600</v>
+        <v>304000</v>
       </c>
       <c r="G57" s="3">
-        <v>301400</v>
+        <v>351300</v>
       </c>
       <c r="H57" s="3">
-        <v>291500</v>
+        <v>310300</v>
       </c>
       <c r="I57" s="3">
+        <v>309000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>298900</v>
+      </c>
+      <c r="K57" s="3">
         <v>330700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>282300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>268200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>257200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>296200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>239100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>215100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>202600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>223300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>263600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>254500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>207400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>233800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>326000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>247300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>238500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>244400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>346500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>270000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>238600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>264200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>248200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>232300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>219500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>342500</v>
+        <v>47900</v>
       </c>
       <c r="E58" s="3">
-        <v>262800</v>
+        <v>188600</v>
       </c>
       <c r="F58" s="3">
-        <v>136900</v>
+        <v>351200</v>
       </c>
       <c r="G58" s="3">
-        <v>261600</v>
+        <v>269500</v>
       </c>
       <c r="H58" s="3">
-        <v>264900</v>
+        <v>140400</v>
       </c>
       <c r="I58" s="3">
+        <v>268300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>271700</v>
+      </c>
+      <c r="K58" s="3">
         <v>132900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>137300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>128900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>131400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>80100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>82400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>75900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>76900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>8100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>9400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>7700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>11700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>7700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>11900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>8100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>7500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>8100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>207400</v>
+        <v>274800</v>
       </c>
       <c r="E59" s="3">
-        <v>289400</v>
+        <v>152600</v>
       </c>
       <c r="F59" s="3">
-        <v>234700</v>
+        <v>212700</v>
       </c>
       <c r="G59" s="3">
-        <v>182700</v>
+        <v>296800</v>
       </c>
       <c r="H59" s="3">
-        <v>222000</v>
+        <v>240700</v>
       </c>
       <c r="I59" s="3">
+        <v>187300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>227600</v>
+      </c>
+      <c r="K59" s="3">
         <v>220700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>213600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>178500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>198100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>249200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>155000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>146400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>176000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>204700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>214200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>137700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>209000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>285700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>273100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>218600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>178900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>300100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>238400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>99100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>157200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>262900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>279700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>141200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>204600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>846400</v>
+        <v>649500</v>
       </c>
       <c r="E60" s="3">
-        <v>894800</v>
+        <v>627200</v>
       </c>
       <c r="F60" s="3">
-        <v>674200</v>
+        <v>867900</v>
       </c>
       <c r="G60" s="3">
-        <v>745600</v>
+        <v>917500</v>
       </c>
       <c r="H60" s="3">
-        <v>778400</v>
+        <v>691400</v>
       </c>
       <c r="I60" s="3">
+        <v>764600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>798200</v>
+      </c>
+      <c r="K60" s="3">
         <v>684300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>633200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>575700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>586800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>625400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>476500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>437400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>455500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>431600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>485900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>397500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>425800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>524900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>606900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>468800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>424700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>547500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>596600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>376800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>407800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>535200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>535400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>377100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>432200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>658000</v>
+        <v>680700</v>
       </c>
       <c r="E61" s="3">
-        <v>686600</v>
+        <v>680900</v>
       </c>
       <c r="F61" s="3">
-        <v>659200</v>
+        <v>674800</v>
       </c>
       <c r="G61" s="3">
-        <v>670300</v>
+        <v>704100</v>
       </c>
       <c r="H61" s="3">
-        <v>688600</v>
+        <v>676000</v>
       </c>
       <c r="I61" s="3">
+        <v>687400</v>
+      </c>
+      <c r="J61" s="3">
+        <v>706100</v>
+      </c>
+      <c r="K61" s="3">
         <v>742100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>682300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>610600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>595500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>607200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>580900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>559600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>555500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>592100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>638400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>692800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>668900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>717900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>715700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>656800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>663800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>650400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>629200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>590800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>619200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>623500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>649100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>679800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>692400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>256400</v>
+        <v>244300</v>
       </c>
       <c r="E62" s="3">
-        <v>272100</v>
+        <v>261200</v>
       </c>
       <c r="F62" s="3">
-        <v>220000</v>
+        <v>262900</v>
       </c>
       <c r="G62" s="3">
-        <v>208700</v>
+        <v>279000</v>
       </c>
       <c r="H62" s="3">
-        <v>218500</v>
+        <v>225600</v>
       </c>
       <c r="I62" s="3">
+        <v>214000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>224100</v>
+      </c>
+      <c r="K62" s="3">
         <v>262400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>176700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>178900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>206000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>205400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>168300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>131100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>132100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>138100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>134900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>164000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>129500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>127200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>207600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>173500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>149100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>145800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>220400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>189900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>181100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>172900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>189700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>146700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>150200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1760700</v>
+        <v>1574500</v>
       </c>
       <c r="E66" s="3">
-        <v>1853400</v>
+        <v>1569400</v>
       </c>
       <c r="F66" s="3">
-        <v>1553400</v>
+        <v>1805600</v>
       </c>
       <c r="G66" s="3">
-        <v>1624600</v>
+        <v>1900600</v>
       </c>
       <c r="H66" s="3">
-        <v>1685500</v>
+        <v>1593000</v>
       </c>
       <c r="I66" s="3">
+        <v>1666000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1728400</v>
+      </c>
+      <c r="K66" s="3">
         <v>1688800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1492200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1365200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1388400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1438100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1225700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1128100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1143200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1161800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1259200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1254400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1224200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1370000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1530200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1299100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1237600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1343700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>62000</v>
+        <v>-79000</v>
       </c>
       <c r="E72" s="3">
-        <v>35000</v>
+        <v>-29700</v>
       </c>
       <c r="F72" s="3">
-        <v>67000</v>
+        <v>63600</v>
       </c>
       <c r="G72" s="3">
-        <v>70300</v>
+        <v>35900</v>
       </c>
       <c r="H72" s="3">
-        <v>76700</v>
+        <v>68700</v>
       </c>
       <c r="I72" s="3">
+        <v>72100</v>
+      </c>
+      <c r="J72" s="3">
+        <v>78600</v>
+      </c>
+      <c r="K72" s="3">
         <v>67800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>101100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>202400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>259000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>265800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>292100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>409300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>435200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>363400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>410200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>511700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>570600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>522500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>540400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>553600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>554200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>518600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>498700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>556100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>565500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>590400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>577100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>562200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>582100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>122900</v>
+        <v>190100</v>
       </c>
       <c r="E76" s="3">
-        <v>92100</v>
+        <v>240400</v>
       </c>
       <c r="F76" s="3">
-        <v>133000</v>
+        <v>126000</v>
       </c>
       <c r="G76" s="3">
-        <v>133700</v>
+        <v>94500</v>
       </c>
       <c r="H76" s="3">
-        <v>140400</v>
+        <v>136400</v>
       </c>
       <c r="I76" s="3">
+        <v>137100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>144000</v>
+      </c>
+      <c r="K76" s="3">
         <v>129500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>163200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>262400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>306100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>312600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>338100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>452600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>475100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>401400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>428500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>551100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>628700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>560000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>587600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>604200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>598000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>571200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>552200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>629000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>624100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>649100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>626200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>602800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>615800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>26100</v>
+        <v>-47600</v>
       </c>
       <c r="E81" s="3">
-        <v>-33000</v>
+        <v>-93800</v>
       </c>
       <c r="F81" s="3">
-        <v>-3700</v>
+        <v>26700</v>
       </c>
       <c r="G81" s="3">
-        <v>-7100</v>
+        <v>-33800</v>
       </c>
       <c r="H81" s="3">
-        <v>8100</v>
+        <v>-3800</v>
       </c>
       <c r="I81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-33900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-90700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-34400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-19700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-133600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-21600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>74800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-35800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-44500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-30400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>47700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-31400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>10200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>35400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>8800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>8900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>12500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>31600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>23100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7399,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>66100</v>
       </c>
       <c r="F83" s="3">
-        <v>61400</v>
+        <v>71700</v>
       </c>
       <c r="G83" s="3">
-        <v>59400</v>
+        <v>66900</v>
       </c>
       <c r="H83" s="3">
-        <v>62200</v>
+        <v>62900</v>
       </c>
       <c r="I83" s="3">
+        <v>60900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>63700</v>
+      </c>
+      <c r="K83" s="3">
         <v>55800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>53400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>53300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>52400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>49200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>41400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>41200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>42300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>41800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>47000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>48000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>47600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>48900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>47000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>44300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>48100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>50100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>45800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>45300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>52300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>50400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>41500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>42900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>48800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-59500</v>
+        <v>165100</v>
       </c>
       <c r="E89" s="3">
-        <v>27500</v>
+        <v>-19800</v>
       </c>
       <c r="F89" s="3">
-        <v>139800</v>
+        <v>-61100</v>
       </c>
       <c r="G89" s="3">
-        <v>69200</v>
+        <v>28200</v>
       </c>
       <c r="H89" s="3">
-        <v>-78700</v>
+        <v>143400</v>
       </c>
       <c r="I89" s="3">
+        <v>70900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-7700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>52600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>28800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-39100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>80600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>30800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>32200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>73700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>35000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-20800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-19600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>212500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>29600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>151600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>130000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>27400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>23400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>231800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>52400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-38500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-141200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-17200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-32600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-104400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-16200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-20600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-75800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-6200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-6900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-39200</v>
+        <v>-8000</v>
       </c>
       <c r="E94" s="3">
-        <v>-147900</v>
+        <v>-24800</v>
       </c>
       <c r="F94" s="3">
-        <v>-7000</v>
+        <v>-40200</v>
       </c>
       <c r="G94" s="3">
-        <v>-14600</v>
+        <v>-151700</v>
       </c>
       <c r="H94" s="3">
-        <v>-39000</v>
+        <v>-7200</v>
       </c>
       <c r="I94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-118700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-23100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-82100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-11500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-63200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-10600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-34400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-23100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-220100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-43100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-24500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-143500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>5300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8142,13 +8610,13 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-15300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-13500</v>
@@ -8157,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-13500</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8166,55 +8634,61 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-14500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-16600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8984,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>76400</v>
+        <v>-146500</v>
       </c>
       <c r="E100" s="3">
-        <v>127700</v>
+        <v>50300</v>
       </c>
       <c r="F100" s="3">
-        <v>-128400</v>
+        <v>78300</v>
       </c>
       <c r="G100" s="3">
+        <v>131000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-131700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>127200</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>130500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-15500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-14100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>49100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-13300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>69800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-37300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-20100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-16600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-15500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-14300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>500</v>
+      </c>
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
+        <v>300</v>
+      </c>
+      <c r="P101" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M101" s="3">
-        <v>300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>700</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="S101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="W101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>9500</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>5400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>12000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>8200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="X101" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>9500</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>9000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-23100</v>
+        <v>8600</v>
       </c>
       <c r="E102" s="3">
-        <v>6200</v>
+        <v>5500</v>
       </c>
       <c r="F102" s="3">
-        <v>2900</v>
+        <v>-23600</v>
       </c>
       <c r="G102" s="3">
-        <v>54600</v>
+        <v>6300</v>
       </c>
       <c r="H102" s="3">
-        <v>8700</v>
+        <v>3000</v>
       </c>
       <c r="I102" s="3">
+        <v>56000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-124100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>32500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>10400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-15200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>32200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>25400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-47200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-14100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-53800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-228200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>161000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>4600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-75400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>7200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>103800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>8300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>179500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>39400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,275 +656,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>186600</v>
+        <v>191800</v>
       </c>
       <c r="E8" s="3">
-        <v>179400</v>
+        <v>179700</v>
       </c>
       <c r="F8" s="3">
-        <v>296300</v>
+        <v>172600</v>
       </c>
       <c r="G8" s="3">
-        <v>206100</v>
+        <v>287600</v>
       </c>
       <c r="H8" s="3">
-        <v>219500</v>
+        <v>191700</v>
       </c>
       <c r="I8" s="3">
-        <v>223100</v>
+        <v>212600</v>
       </c>
       <c r="J8" s="3">
+        <v>210400</v>
+      </c>
+      <c r="K8" s="3">
         <v>219700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>183900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>151600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>189600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>230000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>160300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>116600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>141100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>202500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>128900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>99400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>164700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>229800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>184700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>185900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>202500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>275500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>178300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>157200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>190200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>231400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>187400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>229400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>167500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>207900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
+      <c r="E9" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>19600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>27700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="I9" s="3">
+        <v>44400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>33300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>191800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>153000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>259900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>191700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>168300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>177100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,52 +1358,55 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-36100</v>
       </c>
       <c r="E14" s="3">
-        <v>39800</v>
+        <v>1400</v>
       </c>
       <c r="F14" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
+        <v>37300</v>
+      </c>
+      <c r="G14" s="3">
+        <v>11700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+        <v>-36000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-5700</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>18800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>12400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
@@ -1394,157 +1414,163 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>4600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>25900</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>77100</v>
       </c>
       <c r="E15" s="3">
-        <v>66100</v>
+        <v>64000</v>
       </c>
       <c r="F15" s="3">
-        <v>71700</v>
+        <v>63700</v>
       </c>
       <c r="G15" s="3">
-        <v>66900</v>
+        <v>69600</v>
       </c>
       <c r="H15" s="3">
-        <v>62900</v>
+        <v>62200</v>
       </c>
       <c r="I15" s="3">
         <v>60900</v>
       </c>
       <c r="J15" s="3">
+        <v>57400</v>
+      </c>
+      <c r="K15" s="3">
         <v>63700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>55800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>52400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>49200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>42300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>48000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>48900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>44300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>50100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>45800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>45300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>52300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>50400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>41500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>48800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>229100</v>
+        <v>237200</v>
       </c>
       <c r="E17" s="3">
-        <v>266300</v>
+        <v>216700</v>
       </c>
       <c r="F17" s="3">
-        <v>260200</v>
+        <v>219000</v>
       </c>
       <c r="G17" s="3">
-        <v>203800</v>
+        <v>240800</v>
       </c>
       <c r="H17" s="3">
-        <v>219900</v>
+        <v>225500</v>
       </c>
       <c r="I17" s="3">
-        <v>229300</v>
+        <v>214800</v>
       </c>
       <c r="J17" s="3">
+        <v>218600</v>
+      </c>
+      <c r="K17" s="3">
         <v>223400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>188100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>229400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>216700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>223400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>173100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>162200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>166800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>145700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>161000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>146900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>169100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>180000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>169700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>217300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>183500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>217400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>160000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>187500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>180800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>176400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>164000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>175800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>172900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>158300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-42500</v>
+        <v>-45400</v>
       </c>
       <c r="E18" s="3">
-        <v>-86900</v>
+        <v>-37000</v>
       </c>
       <c r="F18" s="3">
-        <v>36100</v>
+        <v>-46300</v>
       </c>
       <c r="G18" s="3">
-        <v>2400</v>
+        <v>46700</v>
       </c>
       <c r="H18" s="3">
-        <v>-400</v>
+        <v>-33800</v>
       </c>
       <c r="I18" s="3">
-        <v>-6200</v>
+        <v>-2200</v>
       </c>
       <c r="J18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-77800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-45600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>56800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-32000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-47500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>49800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>58100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>55000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>53600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>49600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12000</v>
+        <v>-22500</v>
       </c>
       <c r="E20" s="3">
-        <v>-9600</v>
+        <v>4900</v>
       </c>
       <c r="F20" s="3">
-        <v>14200</v>
+        <v>9300</v>
       </c>
       <c r="G20" s="3">
-        <v>-33500</v>
+        <v>-13600</v>
       </c>
       <c r="H20" s="3">
-        <v>11700</v>
+        <v>31500</v>
       </c>
       <c r="I20" s="3">
-        <v>10400</v>
+        <v>-7100</v>
       </c>
       <c r="J20" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="K20" s="3">
         <v>26600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-30500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-29900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>28800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-26700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>27300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-192800</v>
+        <v>54200</v>
       </c>
       <c r="E21" s="3">
-        <v>-30400</v>
+        <v>22100</v>
       </c>
       <c r="F21" s="3">
-        <v>122000</v>
+        <v>8000</v>
       </c>
       <c r="G21" s="3">
-        <v>35700</v>
+        <v>129900</v>
       </c>
       <c r="H21" s="3">
-        <v>74200</v>
+        <v>-3100</v>
       </c>
       <c r="I21" s="3">
-        <v>65100</v>
+        <v>65800</v>
       </c>
       <c r="J21" s="3">
+        <v>58900</v>
+      </c>
+      <c r="K21" s="3">
         <v>86600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-54300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>56400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>128000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>124600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>60000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>65400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>104800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>68200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>61600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>108000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>79400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>98100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>39700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>89700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="3">
+        <v>12100</v>
       </c>
       <c r="E22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="H22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I22" s="3">
         <v>13100</v>
       </c>
-      <c r="F22" s="3">
-        <v>14600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>11900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>11700</v>
-      </c>
       <c r="J22" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K22" s="3">
         <v>10700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>6700</v>
       </c>
       <c r="P22" s="3">
         <v>6700</v>
       </c>
       <c r="Q22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R22" s="3">
         <v>6100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>6900</v>
       </c>
       <c r="U22" s="3">
         <v>6900</v>
       </c>
       <c r="V22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W22" s="3">
         <v>6500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7100</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-54500</v>
+        <v>2200</v>
       </c>
       <c r="E23" s="3">
-        <v>-109700</v>
+        <v>-52500</v>
       </c>
       <c r="F23" s="3">
-        <v>35700</v>
+        <v>-105500</v>
       </c>
       <c r="G23" s="3">
-        <v>-43000</v>
+        <v>34700</v>
       </c>
       <c r="H23" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
-        <v>-7500</v>
-      </c>
       <c r="J23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="K23" s="3">
         <v>12100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-117500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-44500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>79800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-32000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-56800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-38000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>70600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>11600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>49300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>22300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>49600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>33800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-6900</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
-        <v>-15800</v>
+        <v>-6700</v>
       </c>
       <c r="F24" s="3">
-        <v>9000</v>
+        <v>-15200</v>
       </c>
       <c r="G24" s="3">
-        <v>-9200</v>
+        <v>8700</v>
       </c>
       <c r="H24" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-26900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-8500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>11100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-47600</v>
+        <v>1800</v>
       </c>
       <c r="E26" s="3">
-        <v>-93800</v>
+        <v>-45800</v>
       </c>
       <c r="F26" s="3">
-        <v>26700</v>
+        <v>-90300</v>
       </c>
       <c r="G26" s="3">
-        <v>-33800</v>
+        <v>26000</v>
       </c>
       <c r="H26" s="3">
-        <v>-3800</v>
+        <v>-31400</v>
       </c>
       <c r="I26" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="J26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K26" s="3">
         <v>8300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-90700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>84000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-31900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-45500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>53200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>35400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>38200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>31600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-47600</v>
+        <v>1800</v>
       </c>
       <c r="E27" s="3">
-        <v>-93800</v>
+        <v>-45800</v>
       </c>
       <c r="F27" s="3">
-        <v>26700</v>
+        <v>-90300</v>
       </c>
       <c r="G27" s="3">
-        <v>-33800</v>
+        <v>26000</v>
       </c>
       <c r="H27" s="3">
-        <v>-3800</v>
+        <v>-31400</v>
       </c>
       <c r="I27" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="J27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K27" s="3">
         <v>8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-90700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>84000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-45500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-24300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>53200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>38200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>31600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,37 +2783,40 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2767,31 +2828,31 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-79900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-2700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-9200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-3900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-6200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-5400</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2799,21 +2860,21 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12000</v>
+        <v>22500</v>
       </c>
       <c r="E32" s="3">
-        <v>9600</v>
+        <v>-4900</v>
       </c>
       <c r="F32" s="3">
-        <v>-14200</v>
+        <v>-9300</v>
       </c>
       <c r="G32" s="3">
-        <v>33500</v>
+        <v>13600</v>
       </c>
       <c r="H32" s="3">
-        <v>-11700</v>
+        <v>-31500</v>
       </c>
       <c r="I32" s="3">
-        <v>-10400</v>
+        <v>7100</v>
       </c>
       <c r="J32" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-26600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>30500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>29900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-28800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>26700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-27300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-47600</v>
+        <v>1800</v>
       </c>
       <c r="E33" s="3">
-        <v>-93800</v>
+        <v>-45800</v>
       </c>
       <c r="F33" s="3">
-        <v>26700</v>
+        <v>-90300</v>
       </c>
       <c r="G33" s="3">
-        <v>-33800</v>
+        <v>26000</v>
       </c>
       <c r="H33" s="3">
-        <v>-3800</v>
+        <v>-31400</v>
       </c>
       <c r="I33" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="J33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K33" s="3">
         <v>8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-90700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-133600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-35800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-44500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>47700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>31600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-47600</v>
+        <v>1800</v>
       </c>
       <c r="E35" s="3">
-        <v>-93800</v>
+        <v>-45800</v>
       </c>
       <c r="F35" s="3">
-        <v>26700</v>
+        <v>-90300</v>
       </c>
       <c r="G35" s="3">
-        <v>-33800</v>
+        <v>26000</v>
       </c>
       <c r="H35" s="3">
-        <v>-3800</v>
+        <v>-31400</v>
       </c>
       <c r="I35" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="J35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K35" s="3">
         <v>8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-90700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-133600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-35800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-44500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>47700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>31600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>96500</v>
+        <v>200500</v>
       </c>
       <c r="E41" s="3">
-        <v>87900</v>
+        <v>93000</v>
       </c>
       <c r="F41" s="3">
-        <v>82400</v>
+        <v>84600</v>
       </c>
       <c r="G41" s="3">
-        <v>106100</v>
+        <v>80000</v>
       </c>
       <c r="H41" s="3">
-        <v>99800</v>
+        <v>98600</v>
       </c>
       <c r="I41" s="3">
-        <v>96800</v>
+        <v>96600</v>
       </c>
       <c r="J41" s="3">
+        <v>91200</v>
+      </c>
+      <c r="K41" s="3">
         <v>40700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>118800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>125000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>137300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>94400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>69700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>62900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>120100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>191300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>435300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>258100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>251500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>326900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>312900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>209100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>202600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>282000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>378600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>201000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>161600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3725,16 +3815,16 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3814,715 +3904,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>104300</v>
+        <v>117000</v>
       </c>
       <c r="E43" s="3">
-        <v>122600</v>
+        <v>100500</v>
       </c>
       <c r="F43" s="3">
-        <v>190600</v>
+        <v>118000</v>
       </c>
       <c r="G43" s="3">
-        <v>115400</v>
+        <v>185000</v>
       </c>
       <c r="H43" s="3">
-        <v>117800</v>
+        <v>107300</v>
       </c>
       <c r="I43" s="3">
-        <v>170100</v>
+        <v>114000</v>
       </c>
       <c r="J43" s="3">
+        <v>160400</v>
+      </c>
+      <c r="K43" s="3">
         <v>232000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>132900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>117200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>129200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>156100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>107000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>114800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>101500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>152600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>116300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>199300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>113300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>144100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>125300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>92300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>247800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>164900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>122400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>218300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>152200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>160500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>111200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>135300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>114100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>163800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4600</v>
+        <v>16700</v>
       </c>
       <c r="E44" s="3">
-        <v>4900</v>
+        <v>4500</v>
       </c>
       <c r="F44" s="3">
-        <v>5300</v>
+        <v>4700</v>
       </c>
       <c r="G44" s="3">
-        <v>6600</v>
+        <v>5100</v>
       </c>
       <c r="H44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R44" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T44" s="3">
         <v>4200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="U44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V44" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W44" s="3">
         <v>3500</v>
       </c>
-      <c r="J44" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K44" s="3">
-        <v>4800</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="X44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z44" s="3">
         <v>2800</v>
       </c>
-      <c r="M44" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N44" s="3">
-        <v>3600</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="AA44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AB44" s="3">
         <v>3500</v>
-      </c>
-      <c r="P44" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="R44" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S44" s="3">
-        <v>4200</v>
-      </c>
-      <c r="T44" s="3">
-        <v>2700</v>
-      </c>
-      <c r="U44" s="3">
-        <v>3200</v>
-      </c>
-      <c r="V44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="W44" s="3">
-        <v>3600</v>
-      </c>
-      <c r="X44" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>1800</v>
       </c>
       <c r="AC44" s="3">
         <v>1800</v>
       </c>
       <c r="AD44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AE44" s="3">
         <v>2500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>24600</v>
+        <v>2400</v>
       </c>
       <c r="F45" s="3">
-        <v>38600</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>56500</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
-        <v>32500</v>
+        <v>3800</v>
       </c>
       <c r="I45" s="3">
-        <v>29500</v>
+        <v>5300</v>
       </c>
       <c r="J45" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K45" s="3">
         <v>44600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>18000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>232600</v>
+        <v>383100</v>
       </c>
       <c r="E46" s="3">
-        <v>240000</v>
+        <v>224000</v>
       </c>
       <c r="F46" s="3">
-        <v>316900</v>
+        <v>231000</v>
       </c>
       <c r="G46" s="3">
-        <v>284600</v>
+        <v>307600</v>
       </c>
       <c r="H46" s="3">
-        <v>254200</v>
+        <v>264700</v>
       </c>
       <c r="I46" s="3">
-        <v>299800</v>
+        <v>246200</v>
       </c>
       <c r="J46" s="3">
+        <v>282700</v>
+      </c>
+      <c r="K46" s="3">
         <v>321600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>223800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>303500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>278400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>295400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>269900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>264200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>221400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>271400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>215800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>274200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>252100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>303100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>341700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>549500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>509300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>420600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>453500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>534500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>366700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>369100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>399100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>520200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>322100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>332900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>36600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>32400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>32100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>59100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>29300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>28200</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K47" s="3">
         <v>27900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>43900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>25300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>40200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>29700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>53300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>56500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>55400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>57100</v>
-      </c>
-      <c r="X47" s="3">
-        <v>14000</v>
       </c>
       <c r="Y47" s="3">
         <v>14000</v>
       </c>
       <c r="Z47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>14400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>16200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>20100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>19700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>372700</v>
+        <v>366400</v>
       </c>
       <c r="E48" s="3">
-        <v>370800</v>
+        <v>334000</v>
       </c>
       <c r="F48" s="3">
-        <v>371700</v>
+        <v>331900</v>
       </c>
       <c r="G48" s="3">
-        <v>374400</v>
+        <v>335600</v>
       </c>
       <c r="H48" s="3">
-        <v>370100</v>
+        <v>323800</v>
       </c>
       <c r="I48" s="3">
-        <v>348700</v>
+        <v>333000</v>
       </c>
       <c r="J48" s="3">
+        <v>303900</v>
+      </c>
+      <c r="K48" s="3">
         <v>350300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>343600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>341700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>333200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>335000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>344400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>337500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>327100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>323100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>328800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>341400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>378900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>386600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>384000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>383500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>346300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>344300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>345200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>353000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>352800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>661600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>340100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>337400</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>339900</v>
       </c>
       <c r="AH48" s="3">
         <v>339900</v>
       </c>
       <c r="AI48" s="3">
+        <v>339900</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1099100</v>
+        <v>574200</v>
       </c>
       <c r="E49" s="3">
-        <v>1151200</v>
+        <v>542100</v>
       </c>
       <c r="F49" s="3">
-        <v>1210500</v>
+        <v>542200</v>
       </c>
       <c r="G49" s="3">
-        <v>1268600</v>
+        <v>545600</v>
       </c>
       <c r="H49" s="3">
-        <v>1066000</v>
+        <v>521000</v>
       </c>
       <c r="I49" s="3">
-        <v>1106600</v>
+        <v>543300</v>
       </c>
       <c r="J49" s="3">
+        <v>527800</v>
+      </c>
+      <c r="K49" s="3">
         <v>1143600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1178400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>951100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>963400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1007700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1075800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>936100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>926100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>910700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>923400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>945600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1044600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1034400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1071500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1088000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>956700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>976700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1013600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>972200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>935900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>931700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>23600</v>
+        <v>26500</v>
       </c>
       <c r="E52" s="3">
-        <v>15300</v>
+        <v>25400</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>25800</v>
       </c>
       <c r="G52" s="3">
-        <v>8400</v>
+        <v>25500</v>
       </c>
       <c r="H52" s="3">
-        <v>9800</v>
+        <v>24500</v>
       </c>
       <c r="I52" s="3">
-        <v>19800</v>
+        <v>34900</v>
       </c>
       <c r="J52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="K52" s="3">
         <v>29100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>47800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>73000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>65500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>73200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>73500</v>
       </c>
       <c r="V52" s="3">
         <v>73500</v>
       </c>
       <c r="W52" s="3">
+        <v>73500</v>
+      </c>
+      <c r="X52" s="3">
         <v>75800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>82700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>77000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>79500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>88100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>104000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>102600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>177500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>186700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>192900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>194100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1764600</v>
+        <v>2202100</v>
       </c>
       <c r="E54" s="3">
-        <v>1809800</v>
+        <v>1699500</v>
       </c>
       <c r="F54" s="3">
-        <v>1931600</v>
+        <v>1741900</v>
       </c>
       <c r="G54" s="3">
-        <v>1995100</v>
+        <v>1875000</v>
       </c>
       <c r="H54" s="3">
-        <v>1729400</v>
+        <v>1855400</v>
       </c>
       <c r="I54" s="3">
-        <v>1803100</v>
+        <v>1674800</v>
       </c>
       <c r="J54" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1872500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1818400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1655400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1627600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1694500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1750700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1563800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1580700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1618300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1563300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1687700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1805500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1852900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1930100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2117700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1903300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1835600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1914900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>326800</v>
+        <v>291600</v>
       </c>
       <c r="E57" s="3">
-        <v>286100</v>
+        <v>209100</v>
       </c>
       <c r="F57" s="3">
-        <v>304000</v>
+        <v>183500</v>
       </c>
       <c r="G57" s="3">
-        <v>351300</v>
+        <v>202500</v>
       </c>
       <c r="H57" s="3">
-        <v>310300</v>
+        <v>224800</v>
       </c>
       <c r="I57" s="3">
-        <v>309000</v>
+        <v>180500</v>
       </c>
       <c r="J57" s="3">
+        <v>167100</v>
+      </c>
+      <c r="K57" s="3">
         <v>298900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>330700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>282300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>268200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>257200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>296200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>239100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>215100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>202600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>223300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>263600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>254500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>207400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>233800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>326000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>247300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>238500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>244400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>346500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>270000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>238600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>264200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>248200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>232300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>219500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>47900</v>
+        <v>312000</v>
       </c>
       <c r="E58" s="3">
-        <v>188600</v>
+        <v>46100</v>
       </c>
       <c r="F58" s="3">
-        <v>351200</v>
+        <v>181500</v>
       </c>
       <c r="G58" s="3">
-        <v>269500</v>
+        <v>340900</v>
       </c>
       <c r="H58" s="3">
-        <v>140400</v>
+        <v>250600</v>
       </c>
       <c r="I58" s="3">
-        <v>268300</v>
+        <v>136000</v>
       </c>
       <c r="J58" s="3">
+        <v>252900</v>
+      </c>
+      <c r="K58" s="3">
         <v>271700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>132900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>137300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>128900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>131400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>80100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>82400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>75900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>76900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>274800</v>
+        <v>328300</v>
       </c>
       <c r="E59" s="3">
-        <v>152600</v>
+        <v>276900</v>
       </c>
       <c r="F59" s="3">
-        <v>212700</v>
+        <v>161400</v>
       </c>
       <c r="G59" s="3">
-        <v>296800</v>
+        <v>206400</v>
       </c>
       <c r="H59" s="3">
-        <v>240700</v>
+        <v>278700</v>
       </c>
       <c r="I59" s="3">
-        <v>187300</v>
+        <v>247700</v>
       </c>
       <c r="J59" s="3">
+        <v>194500</v>
+      </c>
+      <c r="K59" s="3">
         <v>227600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>220700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>213600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>178500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>198100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>249200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>155000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>146400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>176000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>204700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>214200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>137700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>209000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>285700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>273100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>218600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>178900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>300100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>238400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>99100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>157200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>262900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>279700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>141200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>204600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>649500</v>
+        <v>1050600</v>
       </c>
       <c r="E60" s="3">
-        <v>627200</v>
+        <v>625600</v>
       </c>
       <c r="F60" s="3">
-        <v>867900</v>
+        <v>603700</v>
       </c>
       <c r="G60" s="3">
-        <v>917500</v>
+        <v>842500</v>
       </c>
       <c r="H60" s="3">
-        <v>691400</v>
+        <v>853300</v>
       </c>
       <c r="I60" s="3">
-        <v>764600</v>
+        <v>669500</v>
       </c>
       <c r="J60" s="3">
+        <v>720900</v>
+      </c>
+      <c r="K60" s="3">
         <v>798200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>684300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>633200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>575700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>586800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>625400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>476500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>437400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>455500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>431600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>485900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>397500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>425800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>524900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>606900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>468800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>424700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>547500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>596600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>376800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>407800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>535200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>535400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>377100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>432200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>680700</v>
+        <v>656700</v>
       </c>
       <c r="E61" s="3">
-        <v>680900</v>
+        <v>655600</v>
       </c>
       <c r="F61" s="3">
-        <v>674800</v>
+        <v>655400</v>
       </c>
       <c r="G61" s="3">
-        <v>704100</v>
+        <v>655000</v>
       </c>
       <c r="H61" s="3">
-        <v>676000</v>
+        <v>654800</v>
       </c>
       <c r="I61" s="3">
-        <v>687400</v>
+        <v>654700</v>
       </c>
       <c r="J61" s="3">
+        <v>648100</v>
+      </c>
+      <c r="K61" s="3">
         <v>706100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>742100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>682300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>610600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>595500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>607200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>580900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>559600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>555500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>592100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>638400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>692800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>668900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>717900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>715700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>656800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>663800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>650400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>629200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>590800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>619200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>623500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>649100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>679800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>692400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>244300</v>
+        <v>286500</v>
       </c>
       <c r="E62" s="3">
-        <v>261200</v>
+        <v>228500</v>
       </c>
       <c r="F62" s="3">
-        <v>262900</v>
+        <v>242800</v>
       </c>
       <c r="G62" s="3">
-        <v>279000</v>
+        <v>243800</v>
       </c>
       <c r="H62" s="3">
-        <v>225600</v>
+        <v>249900</v>
       </c>
       <c r="I62" s="3">
-        <v>214000</v>
+        <v>205800</v>
       </c>
       <c r="J62" s="3">
+        <v>194600</v>
+      </c>
+      <c r="K62" s="3">
         <v>224100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>262400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>176700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>178900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>206000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>205400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>168300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>131100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>132100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>138100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>134900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>164000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>129500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>127200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>207600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>173500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>149100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>145800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>220400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>189900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>181100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>172900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>189700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>146700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>150200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1574500</v>
+        <v>2003500</v>
       </c>
       <c r="E66" s="3">
-        <v>1569400</v>
+        <v>1516400</v>
       </c>
       <c r="F66" s="3">
-        <v>1805600</v>
+        <v>1510500</v>
       </c>
       <c r="G66" s="3">
-        <v>1900600</v>
+        <v>1752700</v>
       </c>
       <c r="H66" s="3">
-        <v>1593000</v>
+        <v>1767500</v>
       </c>
       <c r="I66" s="3">
-        <v>1666000</v>
+        <v>1542700</v>
       </c>
       <c r="J66" s="3">
+        <v>1570700</v>
+      </c>
+      <c r="K66" s="3">
         <v>1728400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1688800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1492200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1365200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1388400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1438100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1225700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1128100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1143200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1161800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1259200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1254400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1224200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1370000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1530200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1299100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1237600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1343700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-79000</v>
+        <v>-412200</v>
       </c>
       <c r="E72" s="3">
-        <v>-29700</v>
+        <v>-390800</v>
       </c>
       <c r="F72" s="3">
-        <v>63600</v>
+        <v>-343100</v>
       </c>
       <c r="G72" s="3">
-        <v>35900</v>
+        <v>-255500</v>
       </c>
       <c r="H72" s="3">
-        <v>68700</v>
+        <v>-270500</v>
       </c>
       <c r="I72" s="3">
-        <v>72100</v>
+        <v>-249900</v>
       </c>
       <c r="J72" s="3">
+        <v>-240100</v>
+      </c>
+      <c r="K72" s="3">
         <v>78600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>67800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>101100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>202400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>259000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>265800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>292100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>409300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>435200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>363400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>410200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>511700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>570600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>522500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>540400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>553600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>554200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>518600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>498700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>556100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>565500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>590400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>577100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>562200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>582100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>190100</v>
+        <v>198600</v>
       </c>
       <c r="E76" s="3">
-        <v>240400</v>
+        <v>183100</v>
       </c>
       <c r="F76" s="3">
-        <v>126000</v>
+        <v>231400</v>
       </c>
       <c r="G76" s="3">
-        <v>94500</v>
+        <v>122300</v>
       </c>
       <c r="H76" s="3">
-        <v>136400</v>
+        <v>87800</v>
       </c>
       <c r="I76" s="3">
-        <v>137100</v>
+        <v>132100</v>
       </c>
       <c r="J76" s="3">
+        <v>129300</v>
+      </c>
+      <c r="K76" s="3">
         <v>144000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>129500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>163200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>262400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>306100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>312600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>338100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>452600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>475100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>401400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>428500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>551100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>628700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>560000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>587600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>604200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>598000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>571200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>552200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>629000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>624100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>649100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>626200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>602800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>615800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-47600</v>
+        <v>1800</v>
       </c>
       <c r="E81" s="3">
-        <v>-93800</v>
+        <v>-45800</v>
       </c>
       <c r="F81" s="3">
-        <v>26700</v>
+        <v>-90300</v>
       </c>
       <c r="G81" s="3">
-        <v>-33800</v>
+        <v>26000</v>
       </c>
       <c r="H81" s="3">
-        <v>-3800</v>
+        <v>-31400</v>
       </c>
       <c r="I81" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="J81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K81" s="3">
         <v>8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-90700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-133600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-35800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-44500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>47700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>31600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>5000</v>
       </c>
       <c r="E83" s="3">
-        <v>66100</v>
+        <v>4200</v>
       </c>
       <c r="F83" s="3">
-        <v>71700</v>
+        <v>4300</v>
       </c>
       <c r="G83" s="3">
-        <v>66900</v>
+        <v>4300</v>
       </c>
       <c r="H83" s="3">
-        <v>62900</v>
+        <v>3900</v>
       </c>
       <c r="I83" s="3">
-        <v>60900</v>
+        <v>4300</v>
       </c>
       <c r="J83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K83" s="3">
         <v>63700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>53400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>52400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>49200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>41800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>48000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>48900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>47000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>44300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>45800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>45300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>165100</v>
+        <v>17800</v>
       </c>
       <c r="E89" s="3">
-        <v>-19800</v>
+        <v>159100</v>
       </c>
       <c r="F89" s="3">
-        <v>-61100</v>
+        <v>-19100</v>
       </c>
       <c r="G89" s="3">
-        <v>28200</v>
+        <v>-59300</v>
       </c>
       <c r="H89" s="3">
-        <v>143400</v>
+        <v>26200</v>
       </c>
       <c r="I89" s="3">
-        <v>70900</v>
+        <v>138800</v>
       </c>
       <c r="J89" s="3">
+        <v>66900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-80700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>52600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-39100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>80600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>73700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>35000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-19600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>212500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>29600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>151600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>130000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>27400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>23400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>231800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>52400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-104400</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-6900</v>
       </c>
-      <c r="E91" s="3">
-        <v>-21600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-38500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-141200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-17200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-32600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-104400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-16200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-20600</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-75800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-12900</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Z91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8000</v>
+        <v>-174900</v>
       </c>
       <c r="E94" s="3">
-        <v>-24800</v>
+        <v>-7700</v>
       </c>
       <c r="F94" s="3">
-        <v>-40200</v>
+        <v>-23800</v>
       </c>
       <c r="G94" s="3">
-        <v>-151700</v>
+        <v>-39000</v>
       </c>
       <c r="H94" s="3">
-        <v>-7200</v>
+        <v>-141000</v>
       </c>
       <c r="I94" s="3">
-        <v>-15000</v>
+        <v>-6900</v>
       </c>
       <c r="J94" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-40000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-82100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-43600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-63200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-220100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-143500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,50 +8819,51 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-15300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-13500</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-13500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8640,11 +8874,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-14500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8652,11 +8886,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8664,11 +8898,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8676,19 +8910,22 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-146500</v>
+        <v>267900</v>
       </c>
       <c r="E100" s="3">
-        <v>50300</v>
+        <v>-141100</v>
       </c>
       <c r="F100" s="3">
-        <v>78300</v>
+        <v>48500</v>
       </c>
       <c r="G100" s="3">
-        <v>131000</v>
+        <v>76000</v>
       </c>
       <c r="H100" s="3">
-        <v>-131700</v>
+        <v>121800</v>
       </c>
       <c r="I100" s="3">
+        <v>-127500</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>130500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>49100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>69800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-37300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-20100</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-500</v>
       </c>
       <c r="W100" s="3">
         <v>-500</v>
       </c>
       <c r="X100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-14300</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-100</v>
       </c>
       <c r="AE100" s="3">
         <v>-100</v>
       </c>
       <c r="AF100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15700</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>-100</v>
       </c>
       <c r="AI100" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2000</v>
+        <v>-1100</v>
       </c>
       <c r="E101" s="3">
-        <v>-200</v>
+        <v>-1500</v>
       </c>
       <c r="F101" s="3">
-        <v>-700</v>
+        <v>300</v>
       </c>
       <c r="G101" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="H101" s="3">
-        <v>-1500</v>
+        <v>3000</v>
       </c>
       <c r="I101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>600</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>500</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
+        <v>700</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="T101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="X101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>9500</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
-        <v>500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>5400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>12000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>8200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>9500</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>8600</v>
+        <v>101900</v>
       </c>
       <c r="E102" s="3">
-        <v>5500</v>
+        <v>8300</v>
       </c>
       <c r="F102" s="3">
-        <v>-23600</v>
+        <v>5300</v>
       </c>
       <c r="G102" s="3">
-        <v>6300</v>
+        <v>-23000</v>
       </c>
       <c r="H102" s="3">
-        <v>3000</v>
+        <v>5900</v>
       </c>
       <c r="I102" s="3">
-        <v>56000</v>
+        <v>2900</v>
       </c>
       <c r="J102" s="3">
+        <v>52800</v>
+      </c>
+      <c r="K102" s="3">
         <v>8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-124100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-47200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-53800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-228200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>161000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-75400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>103800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>179500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>39400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,286 +656,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>248800</v>
+      </c>
+      <c r="E8" s="3">
         <v>191800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>179700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>172600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>287600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>191700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>212600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>210400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>219700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>151600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>189600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>230000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>160300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>116600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>141100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>202500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>128900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>99400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>164700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>229800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>184700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>185900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>202500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>275500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>178300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>157200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>190200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>231400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>187400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>229400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>167500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>207900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
         <v>39100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19600</v>
       </c>
-      <c r="G9" s="3">
-        <v>27700</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="H9" s="3">
+        <v>253000</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
         <v>44400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1011,35 +1017,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E10" s="3">
         <v>191800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>140700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153000</v>
       </c>
-      <c r="G10" s="3">
-        <v>259900</v>
-      </c>
       <c r="H10" s="3">
+        <v>34500</v>
+      </c>
+      <c r="I10" s="3">
         <v>191700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>168300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>177100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,55 +1377,58 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-36100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>37300</v>
       </c>
-      <c r="G14" s="3">
-        <v>11700</v>
-      </c>
       <c r="H14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I14" s="3">
         <v>-36000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>18800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>12400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
@@ -1417,160 +1436,166 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>4600</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>25900</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E15" s="3">
         <v>77100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>64000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>63700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>62200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>57400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>55800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>52400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>49200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>42300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>41800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>42400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>48000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>48900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>47000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>50100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>45800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>52300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>50400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>41500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>48800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E17" s="3">
         <v>237200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>216700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>219000</v>
       </c>
-      <c r="G17" s="3">
-        <v>240800</v>
-      </c>
       <c r="H17" s="3">
+        <v>253000</v>
+      </c>
+      <c r="I17" s="3">
         <v>225500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>214800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>223400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>188100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>229400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>216700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>223400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>173100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>162200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>166800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>145700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>161000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>146900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>169100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>180000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>169700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>217300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>183500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>217400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>160000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>187500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>180800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>176400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>164000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>175800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>172900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>158300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-45400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46300</v>
       </c>
-      <c r="G18" s="3">
-        <v>46700</v>
-      </c>
       <c r="H18" s="3">
+        <v>34500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-33800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-77800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-27100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-45600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>56800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-32000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-47500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>49800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>58100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>55000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>23400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>53600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>49600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>-22500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>31500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>26600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-30500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-29900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>4400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>28800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-26700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>27300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E21" s="3">
         <v>54200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8000</v>
       </c>
-      <c r="G21" s="3">
-        <v>129900</v>
-      </c>
       <c r="H21" s="3">
+        <v>104100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>58900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>86600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-54300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>56400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>128000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>15000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>124600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>60000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>65400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>104800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>68200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>61600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>108000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>79400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>98100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>39700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>89700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E22" s="3">
         <v>12100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12400</v>
       </c>
-      <c r="G22" s="3">
-        <v>13500</v>
-      </c>
       <c r="H22" s="3">
+        <v>21100</v>
+      </c>
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>6700</v>
       </c>
       <c r="Q22" s="3">
         <v>6700</v>
       </c>
       <c r="R22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S22" s="3">
         <v>6100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>6900</v>
       </c>
       <c r="V22" s="3">
         <v>6900</v>
       </c>
       <c r="W22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="X22" s="3">
         <v>6500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-52500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-105500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-117500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-44500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>79800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-32000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-56800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-38000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>70600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>49700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>11600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>49300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>49600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-26900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-10200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-8500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-11300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-13700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-90300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-90700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>84000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-45500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>53200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>35400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>38200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>12500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>31600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-90300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-90700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>84000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-45500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>53200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>38200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>31600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,14 +2872,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2831,31 +2891,31 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-79900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-9200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-3900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-6200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-5400</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2863,21 +2923,21 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>22500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9300</v>
       </c>
-      <c r="G32" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-31500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-26600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>30500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>29900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-4400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-28800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>26700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-27300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-90300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-90700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-133600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-35800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-44500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-30400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>47700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>31600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-90300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-90700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-133600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-35800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-44500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-30400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>47700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>31600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E41" s="3">
         <v>200500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>93000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>84600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>98600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>96600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>118800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>108500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>125000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>137300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>101000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>94400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>69700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>62900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>120100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>137500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>191300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>435300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>258100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>251500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>326900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>312900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>209100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>202600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>282000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>378600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>201000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>161600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,20 +3904,20 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3907,424 +3996,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>188600</v>
+      </c>
+      <c r="E43" s="3">
         <v>117000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>185000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>107300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>114000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>160400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>232000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>132900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>117200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>156100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>107000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>114800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>101500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>152600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>116300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>199300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>113300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>144100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>125300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>92300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>247800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>164900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>122400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>218300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>152200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>160500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>111200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>135300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>114100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E44" s="3">
         <v>16700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3500</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>1800</v>
       </c>
       <c r="AD44" s="3">
         <v>1800</v>
       </c>
       <c r="AE44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AF44" s="3">
         <v>2500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>25700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>18000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>21400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>18900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>359800</v>
+      </c>
+      <c r="E46" s="3">
         <v>383100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>224000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>231000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>307600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>264700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>282700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>321600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>223800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>303500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>278400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>295400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>269900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>264200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>221400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>271400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>215800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>274200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>252100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>303100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>341700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>549500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>509300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>420600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>453500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>534500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>366700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>369100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>399100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>520200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>322100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>332900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4346,297 +4450,306 @@
       <c r="I47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>4700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>43900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>25300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>31500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>40200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>29700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>53300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>56500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>55400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>57100</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>14000</v>
       </c>
       <c r="Z47" s="3">
         <v>14000</v>
       </c>
       <c r="AA47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB47" s="3">
         <v>14400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>14100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>8600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>20100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>19700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E48" s="3">
         <v>366400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>334000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>331900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>335600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>323800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>333000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>303900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>350300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>343600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>341700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>333200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>335000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>344400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>337500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>327100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>323100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>328800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>341400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>378900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>386600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>384000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>383500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>346300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>344300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>345200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>353000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>352800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>661600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>340100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>337400</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>339900</v>
       </c>
       <c r="AI48" s="3">
         <v>339900</v>
       </c>
       <c r="AJ48" s="3">
+        <v>339900</v>
+      </c>
+      <c r="AK48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1184300</v>
+      </c>
+      <c r="E49" s="3">
         <v>574200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>542100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>542200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>545600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>521000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>543300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>527800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1143600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1178400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>951100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>963400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1007700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1075800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>936100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>926100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>910700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>923400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>945600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1044600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1034400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1071500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1088000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>956700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>976700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1013600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>972200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>935900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>931700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E52" s="3">
         <v>26500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>34900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>47800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>73000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>65500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>73200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>73500</v>
       </c>
       <c r="W52" s="3">
         <v>73500</v>
       </c>
       <c r="X52" s="3">
+        <v>73500</v>
+      </c>
+      <c r="Y52" s="3">
         <v>75800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>82700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>77000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>79500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>88400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>88100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>104000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>102600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>177500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>186700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>192900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>194100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2003600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2202100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1699500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1741900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1875000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1855400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1674800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1700000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1872500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1818400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1655400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1627600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1694500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1750700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1563800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1580700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1618300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1563300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1687700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1805500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1852900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1930100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2117700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1903300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1835600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1914900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>372600</v>
+      </c>
+      <c r="E57" s="3">
         <v>291600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>209100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>183500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>202500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>224800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>180500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>167100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>298900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>330700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>282300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>268200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>257200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>296200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>239100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>215100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>202600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>223300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>263600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>254500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>207400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>233800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>326000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>247300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>238500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>244400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>346500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>270000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>238600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>264200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>248200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>232300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>219500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>270900</v>
+      </c>
+      <c r="E58" s="3">
         <v>312000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>46100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>181500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>340900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>250600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>136000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>252900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>271700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>132900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>137300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>128900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>131400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>80100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>82400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>75900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>76900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>224400</v>
+      </c>
+      <c r="E59" s="3">
         <v>328300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>276900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>161400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>206400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>278700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>247700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>194500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>227600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>220700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>213600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>178500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>198100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>249200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>155000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>146400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>176000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>204700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>214200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>137700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>209000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>285700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>273100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>218600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>178900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>300100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>238400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>99100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>157200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>262900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>279700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>141200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>204600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>867900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1050600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>625600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>603700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>842500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>853300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>669500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>720900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>798200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>684300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>633200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>575700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>586800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>625400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>476500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>437400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>455500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>431600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>485900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>397500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>425800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>524900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>606900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>468800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>424700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>547500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>596600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>376800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>407800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>535200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>535400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>377100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>432200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>655700</v>
+      </c>
+      <c r="E61" s="3">
         <v>656700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>655600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>655400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>655000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>654800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>654700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>648100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>706100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>742100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>682300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>610600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>595500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>607200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>580900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>559600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>555500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>592100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>638400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>692800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>668900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>717900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>715700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>656800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>663800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>650400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>629200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>590800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>619200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>623500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>649100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>679800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>692400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>228600</v>
+      </c>
+      <c r="E62" s="3">
         <v>286500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>228500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>242800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>243800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>249900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>205800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>194600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>224100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>262400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>176700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>178900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>206000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>205400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>168300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>131100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>132100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>138100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>134900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>164000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>129500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>127200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>207600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>173500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>149100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>145800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>220400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>189900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>181100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>172900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>189700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>146700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>150200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1757400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2003500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1516400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1510500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1752700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1767500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1542700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1570700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1728400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1688800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1492200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1365200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1388400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1438100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1225700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1128100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1143200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1161800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1259200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1254400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1224200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1370000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1530200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1299100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1237600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1343700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-419200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-412200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-390800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-343100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-255500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-270500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-249900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-240100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>67800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>101100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>202400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>259000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>265800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>292100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>409300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>435200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>363400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>410200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>511700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>570600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>522500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>540400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>553600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>554200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>518600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>498700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>556100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>565500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>590400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>577100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>562200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>582100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>246300</v>
+      </c>
+      <c r="E76" s="3">
         <v>198600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>183100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>231400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>122300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>87800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>132100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>129300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>144000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>129500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>163200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>262400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>306100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>312600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>338100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>452600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>475100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>401400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>428500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>551100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>628700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>560000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>587600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>604200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>598000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>571200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>552200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>629000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>624100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>649100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>626200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>602800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>615800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-90300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-90700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-133600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-35800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-44500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-30400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>47700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>31600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E83" s="3">
         <v>5000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4300</v>
       </c>
       <c r="G83" s="3">
         <v>4300</v>
       </c>
       <c r="H83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>53300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>52400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>49200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>41200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>42300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>41800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>47000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>48000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>47600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>48900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>47000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>45800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>45300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>52300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>50400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>48800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-79200</v>
+      </c>
+      <c r="E89" s="3">
         <v>17800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>159100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-59300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>138800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>66900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-80700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>52600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-39100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>80600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>73700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>35000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>212500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>29600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>151600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>130000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>27400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>23400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>231800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>52400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-104400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-75800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-174900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-39000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-141000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-118700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-82100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-63200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-34400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-220100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-143500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,27 +9079,27 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-15300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-13500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8877,11 +9110,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-14500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -8889,11 +9122,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8901,11 +9134,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8913,19 +9146,22 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E100" s="3">
         <v>267900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-141100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>48500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>76000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>121800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-127500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>130500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>49100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>69800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-37300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-20100</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-500</v>
       </c>
       <c r="X100" s="3">
         <v>-500</v>
       </c>
       <c r="Y100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14300</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-100</v>
       </c>
       <c r="AF100" s="3">
         <v>-100</v>
       </c>
       <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-15700</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ100" s="3">
         <v>-100</v>
       </c>
+      <c r="AK100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-9400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="E102" s="3">
         <v>101900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-124100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-47200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-53800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-228200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>161000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-75400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>103800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>179500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>39400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,295 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>207400</v>
+      </c>
+      <c r="E8" s="3">
         <v>248800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>191800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>179700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>172600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>287600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>191700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>212600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>210400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>219700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>151600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>189600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>230000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>160300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>116600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>141100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>202500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>128900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>99400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>164700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>229800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>184700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>185900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>202500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>275500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>178300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>157200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>190200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>231400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>187400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>229400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>167500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>207900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E9" s="3">
         <v>246000</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
         <v>39100</v>
       </c>
-      <c r="G9" s="3">
-        <v>19600</v>
-      </c>
       <c r="H9" s="3">
+        <v>19100</v>
+      </c>
+      <c r="I9" s="3">
         <v>253000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>44400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1020,38 +1027,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>176600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>191800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>140700</v>
       </c>
-      <c r="G10" s="3">
-        <v>153000</v>
-      </c>
       <c r="H10" s="3">
+        <v>153600</v>
+      </c>
+      <c r="I10" s="3">
         <v>34500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>191700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>168300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>177100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,58 +1397,61 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-36100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>37300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-36000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>18800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>12400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1439,163 +1459,169 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>4600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1600</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>25900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2500</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E15" s="3">
         <v>67200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>77100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>64000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>63700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>62200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>57400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>63700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>52400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>49200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>41800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>42400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>48000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>48900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>47000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>48100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>50100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>52300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>50400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>41500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>42900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>48800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E17" s="3">
         <v>246000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>237200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>216700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>219000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>253000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>225500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>214800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>218600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>223400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>188100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>229400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>216700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>223400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>173100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>162200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>166800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>145700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>161000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>146900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>169100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>180000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>169700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>217300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>183500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>217400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>160000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>187500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>180800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>176400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>164000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>175800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>172900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>158300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-45400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-46300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-77800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-27100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-45600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-25700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>56800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-32000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-47500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>49800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>58100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>55000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>23400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>53600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>49600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>-22500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>31500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>26600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-30500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-29900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>28800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-26700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>27300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E21" s="3">
         <v>70000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>54200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>104100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>65800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>58900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>86600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-54300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>56400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>128000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>124600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>60000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>65400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>104800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>68200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>61600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>108000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>79400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>98100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>39700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>89700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E22" s="3">
         <v>53200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>21100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>6700</v>
       </c>
       <c r="R22" s="3">
         <v>6700</v>
       </c>
       <c r="S22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="T22" s="3">
         <v>6100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5300</v>
-      </c>
-      <c r="V22" s="3">
-        <v>6900</v>
       </c>
       <c r="W22" s="3">
         <v>6900</v>
       </c>
       <c r="X22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>6500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7100</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-43200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-52500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-105500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-44000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-117500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-44500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-52200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>79800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-32000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-56800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-38000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>70600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-42500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>49700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>11600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>49300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>49600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>33800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-26900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-8500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-13700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>14400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>9900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-90300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-90700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-53700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>84000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-45500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-24300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>53200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>38200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>31600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-90300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-90700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-53700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>84000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-45500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-24300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>53200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>38200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>31600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>23100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,14 +2936,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2894,31 +2955,31 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-79900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-2700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-9200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-3900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-6200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2926,21 +2987,21 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>22500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-31500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-26600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>30500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>29900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-28800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>26700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>11200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>8700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-90300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-90700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-133600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>74800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-35800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-44500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-30400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>47700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>31600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>23100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-90300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-90700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-133600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>74800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-35800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-44500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-30400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>47700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>31600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>23100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>94600</v>
+      </c>
+      <c r="E41" s="3">
         <v>119600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>93000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>98600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>155100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>118800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>108500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>125000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>137300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>101000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>94400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>69700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>62900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>120100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>137500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>191300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>435300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>258100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>251500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>326900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>312900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>209100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>202600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>282000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>378600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>201000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>161600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,20 +3997,20 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3999,436 +4089,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>214100</v>
+      </c>
+      <c r="E43" s="3">
         <v>188600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>117000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>118000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>185000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>107300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>114000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>160400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>232000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>132900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>117200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>156100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>107000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>114800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>101500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>152600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>116300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>199300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>113300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>144100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>125300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>92300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>247800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>164900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>122400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>218300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>152200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>160500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>111200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>135300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>114100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>163800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E44" s="3">
         <v>16800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>1800</v>
       </c>
       <c r="AE44" s="3">
         <v>1800</v>
       </c>
       <c r="AF44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG44" s="3">
         <v>2500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>25700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>21400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>18900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E46" s="3">
         <v>359800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>383100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>224000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>231000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>307600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>264700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>282700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>321600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>223800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>303500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>278400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>295400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>269900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>264200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>221400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>271400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>215800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>274200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>252100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>303100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>341700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>549500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>509300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>420600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>453500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>534500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>366700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>369100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>399100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>520200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>322100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>332900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4453,303 +4558,312 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>4700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>50900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>54200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>25300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>31500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>40200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>29700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>53300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>56500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>57100</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>14000</v>
       </c>
       <c r="AA47" s="3">
         <v>14000</v>
       </c>
       <c r="AB47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>14400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>8600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>20100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>371300</v>
+      </c>
+      <c r="E48" s="3">
         <v>343900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>366400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>334000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>331900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>335600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>323800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>333000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>303900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>350300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>343600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>341700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>333200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>335000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>344400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>337500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>327100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>323100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>328800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>341400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>378900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>386600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>384000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>383500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>346300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>344300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>345200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>353000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>352800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>661600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>340100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>337400</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>339900</v>
       </c>
       <c r="AJ48" s="3">
         <v>339900</v>
       </c>
       <c r="AK48" s="3">
+        <v>339900</v>
+      </c>
+      <c r="AL48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1184300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>574200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>542100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>542200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>545600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>521000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>543300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>527800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1143600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1178400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>951100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>963400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1007700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1075800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>936100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>926100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>910700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>923400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>945600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1044600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1034400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1071500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1088000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>956700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>976700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1013600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>972200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>935900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>931700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E52" s="3">
         <v>25000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>34900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>47800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>73000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>65500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>73200</v>
-      </c>
-      <c r="W52" s="3">
-        <v>73500</v>
       </c>
       <c r="X52" s="3">
         <v>73500</v>
       </c>
       <c r="Y52" s="3">
+        <v>73500</v>
+      </c>
+      <c r="Z52" s="3">
         <v>75800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>82700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>77000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>79500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>88400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>88100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>104000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>102600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>177500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>186700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>192900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>194100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2058200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2003600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2202100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1699500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1741900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1875000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1855400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1674800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1700000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1872500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1818400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1655400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1627600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1694500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1750700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1563800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1580700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1618300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1563300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1687700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1805500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1852900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1930100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2117700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1903300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1835600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1914900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>286400</v>
+      </c>
+      <c r="E57" s="3">
         <v>372600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>291600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>209100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>183500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>202500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>224800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>180500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>298900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>330700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>282300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>268200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>257200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>296200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>239100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>215100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>202600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>223300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>263600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>254500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>207400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>233800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>326000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>247300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>238500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>244400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>346500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>270000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>238600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>264200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>248200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>232300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>219500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>275400</v>
+      </c>
+      <c r="E58" s="3">
         <v>270900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>312000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>181500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>340900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>250600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>136000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>252900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>271700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>132900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>137300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>128900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>131400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>80100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>82400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>75900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>76900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>8100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>250400</v>
+      </c>
+      <c r="E59" s="3">
         <v>224400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>328300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>276900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>161400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>206400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>278700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>247700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>194500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>227600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>220700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>213600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>178500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>198100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>249200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>155000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>146400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>176000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>204700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>214200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>137700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>209000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>285700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>273100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>218600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>178900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>238400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>99100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>157200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>262900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>279700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>141200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>204600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>898700</v>
+      </c>
+      <c r="E60" s="3">
         <v>867900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1050600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>625600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>603700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>842500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>853300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>669500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>720900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>798200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>684300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>633200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>575700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>586800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>625400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>476500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>437400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>455500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>431600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>485900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>397500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>425800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>524900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>606900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>468800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>424700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>547500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>596600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>376800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>407800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>535200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>535400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>377100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>432200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>657200</v>
+      </c>
+      <c r="E61" s="3">
         <v>655700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>656700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>655600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>655400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>655000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>654800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>654700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>648100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>706100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>742100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>682300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>610600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>595500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>607200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>580900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>559600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>555500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>592100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>638400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>692800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>668900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>717900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>715700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>656800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>663800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>650400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>629200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>590800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>619200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>623500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>649100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>679800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>692400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>239200</v>
+      </c>
+      <c r="E62" s="3">
         <v>228600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>286500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>228500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>242800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>243800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>249900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>194600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>224100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>262400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>176700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>178900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>206000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>205400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>168300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>132100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>138100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>134900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>164000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>129500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>127200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>207600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>173500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>149100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>145800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>220400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>189900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>181100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>172900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>189700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>146700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>150200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1803100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1757400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2003500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1516400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1510500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1752700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1767500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1542700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1570700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1728400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1688800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1492200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1365200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1388400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1438100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1225700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1128100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1143200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1161800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1259200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1254400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1224200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1370000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1530200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1299100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1237600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1343700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-435600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-419200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-412200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-390800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-343100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-255500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-270500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-249900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-240100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>78600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>67800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>101100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>202400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>259000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>265800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>292100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>409300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>435200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>363400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>410200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>511700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>570600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>522500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>540400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>553600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>554200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>518600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>498700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>556100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>565500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>590400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>577100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>562200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>582100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E76" s="3">
         <v>246300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>198600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>183100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>231400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>122300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>87800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>132100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>129300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>144000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>129500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>163200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>262400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>306100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>312600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>338100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>452600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>475100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>401400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>428500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>551100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>628700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>560000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>587600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>604200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>598000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>571200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>552200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>629000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>624100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>649100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>626200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>602800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>615800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-90300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-90700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-133600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>74800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-35800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-44500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-30400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>47700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>31600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>23100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E83" s="3">
         <v>5300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4300</v>
       </c>
       <c r="H83" s="3">
         <v>4300</v>
       </c>
       <c r="I83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>53400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>53300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>52400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>49200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>41400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>41200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>42300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>41800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>48000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>47600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>47000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>45800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>45300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>52300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>50400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>48800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-79200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>159100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-59300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>138800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>66900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-80700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>52600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>80600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>73700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>35000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>212500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>29600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>151600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>130000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>27400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>23400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>231800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>52400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-104400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-75800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-174900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-141000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-118700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-82100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-63200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-34400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-220100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-43100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-143500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,27 +9316,27 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-15300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-13500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-13500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -9113,11 +9347,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-14500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -9125,11 +9359,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -9137,11 +9371,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -9149,19 +9383,22 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>75000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>267900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-141100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>48500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>76000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>121800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-127500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>130500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>49100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>69800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-37300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-20100</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-500</v>
       </c>
       <c r="Y100" s="3">
         <v>-500</v>
       </c>
       <c r="Z100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-14300</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-100</v>
       </c>
       <c r="AG100" s="3">
         <v>-100</v>
       </c>
       <c r="AH100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-15700</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>-100</v>
       </c>
       <c r="AK100" s="3">
         <v>-100</v>
       </c>
+      <c r="AL100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>101900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-124100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-47200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-53800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-228200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>161000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-75400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>103800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>179500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>39400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,318 +656,331 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>256100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>188700</v>
+      </c>
+      <c r="F8" s="3">
         <v>224900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>207400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>248800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>191800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>179700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>172600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>287600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>191700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>212600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>210400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>219700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>183900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>151600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>189600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>230000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>160300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>116600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>141100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>202500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>128900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>99400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>164700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>229800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>184700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>185900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>202500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>275500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>178300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>157200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>190200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>231400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>187400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>229400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>167500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>207900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F9" s="3">
         <v>56700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>30900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>246000</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J9" s="3">
         <v>41500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>19100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>253000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>44400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>33300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1040,47 +1053,53 @@
       <c r="AM9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>168100</v>
+      </c>
+      <c r="F10" s="3">
         <v>168200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>176600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2800</v>
       </c>
-      <c r="G10" s="3">
-        <v>191800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>171700</v>
+      </c>
+      <c r="J10" s="3">
         <v>138200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>153600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>34500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>191700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>168300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>177100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,8 +1172,14 @@
       <c r="AM10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,8 +1219,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1307,8 +1334,14 @@
       <c r="AM12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,234 +1453,252 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-36100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>37300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-36000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-5700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-2400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>18800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>12400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>25900</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>5</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F15" s="3">
         <v>71300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>64800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>67200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>77100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>64000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>63700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>69600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>62200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>60900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>57400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>63700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>55800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>53400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>53300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>52400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>49200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>41400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>41200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>42300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>41800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>42400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>48000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>47600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>48900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>47000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>44300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>48100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>50100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>45800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>45300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>52300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>50400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>41500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>42900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>48800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1735,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>234100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>231700</v>
+      </c>
+      <c r="F17" s="3">
         <v>239900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>206000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>246000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>237200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>216700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>219000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>253000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>225500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>214800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>218600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>223400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>188100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>229400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>216700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>223400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>173100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>162200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>166800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>145700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>161000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>146900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>169100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>180000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>169700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>217300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>183500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>217400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>160000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>187500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>180800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>176400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>164000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>175800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>172900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>158300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-45400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-37000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-46300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>34500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-8200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-77800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-27100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-12800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-45600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-25700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>56800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-32000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-47500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>49800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>15000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>19000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>58100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>18300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>9400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>55000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>23400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>53600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>49600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,573 +2016,605 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-22400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-6500</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>-22500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>4900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>9300</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>31500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-9700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>26600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-30500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-10500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-5600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>28800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>5300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>27300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>7000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>3000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>2200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F21" s="3">
         <v>78800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>72700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>70000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>54200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>22100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>104100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>65800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>58900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>86600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>21100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-54300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>15700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>56400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>30800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>19900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>128000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>15000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>16900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>124600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>60000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>12000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>65400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>104800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>68200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>4200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>61600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>108000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>98100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>39700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>89700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F22" s="3">
         <v>12000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>12200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>53200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>12100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>9800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>12400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>21100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>13100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>10700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>9200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>9800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>6700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>6700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>5800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>5300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>6900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>6900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>6500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>7700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>7400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>6200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>7000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>6500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>6800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>5600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>6400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>7000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>6500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>7100</v>
       </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-43200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-52500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-105500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>34700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-40000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-7000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>12100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-44000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-117500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-44500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-25100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-52200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-27500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>79800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-32000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-56800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>70600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-42500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>14800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>49700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>11600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>10700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>49300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>22300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>49600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>33800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-8500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-15200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>8700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-8600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-10100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-10200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-8500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-4200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>17400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>14400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>2800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>11100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>18000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>10700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2726,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-34700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-45800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-90300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-31400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>8300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-33900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-34400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-19700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-53700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-18900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>84000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-31900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-45500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>53200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>10200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>35400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>8800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>8900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>38200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>31600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>23100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-34700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-45800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-90300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-31400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>8300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-33900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-34400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-19700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-53700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-18900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>84000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-31900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-45500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>53200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>10200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>35400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>8800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>8900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>38200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>31600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>23100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3083,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3003,17 +3124,17 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3022,56 +3143,56 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-79900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-2700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-9200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-3900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>1000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3081,8 +3202,14 @@
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3321,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,234 +3440,252 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F32" s="3">
         <v>22400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>6500</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>22500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-4900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-9300</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-31500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>9700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-26600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>30500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>29900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>10500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>5600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-28800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-5300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>26700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>3900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>11200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>8700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-34700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-45800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-90300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-31400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-33900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-34400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-19700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-133600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-21600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>74800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-35800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>47700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>10200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>35400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>8800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>8900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>31600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>23100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3797,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-34700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-45800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-90300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-31400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-33900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-34400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-19700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-133600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-21600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>74800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-35800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>47700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>10200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>35400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>8800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>8900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>31600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>23100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4087,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4130,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>108200</v>
+      </c>
+      <c r="F41" s="3">
         <v>118000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>94600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>119600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>200500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>93000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>84600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>80000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>98600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>96600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>91200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>40700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>31100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>155100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>118800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>108500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>125000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>137300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>101000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>94400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>69700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>62900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>120100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>137500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>191300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>435300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>258100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>251500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>326900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>312900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>209100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>202600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>282000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>378600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>201000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>161600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4093,23 +4272,23 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>5300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4185,460 +4364,490 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>236300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>177300</v>
+      </c>
+      <c r="F43" s="3">
         <v>228700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>214100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>188600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>117000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>100500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>118000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>185000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>107300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>114000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>160400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>232000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>132900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>117200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>129200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>156100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>107000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>114800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>101500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>152600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>116300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>199300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>113300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>144100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>125300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>92300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>247800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>164900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>122400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>218300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>152200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>160500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>111200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>135300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>114100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>163800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>24500</v>
+      </c>
+      <c r="F44" s="3">
         <v>17900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>15500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>16800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>16700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>4000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>4800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>4200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>3500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>2800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>2500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>2100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>44600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>55100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>28300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>27000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>27300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>34300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>9600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>16000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>21000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>25700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>9400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>15400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>18000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>21400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>18900</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>700</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>800</v>
       </c>
       <c r="AE45" s="3">
         <v>700</v>
       </c>
       <c r="AF45" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH45" s="3">
         <v>1500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>3600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>3500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>4200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>5200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>6000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>348400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>344500</v>
+      </c>
+      <c r="F46" s="3">
         <v>389100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>349400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>359800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>383100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>224000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>231000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>307600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>264700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>246200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>282700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>321600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>223800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>303500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>278400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>295400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>269900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>264200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>221400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>271400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>215800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>274200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>252100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>303100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>341700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>549500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>509300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>420600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>453500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>534500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>366700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>369100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>399100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>520200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>322100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>332900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4669,315 +4878,333 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3">
         <v>4700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>27900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>24700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>38100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>43900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>50900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>54200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>25300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>31500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>40200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>29700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>53300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>56500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>55400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>57100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>14400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>14100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>6800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>8600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>16200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>20100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>19700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>5600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>405200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>411600</v>
+      </c>
+      <c r="F48" s="3">
         <v>410300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>371300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>343900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>366400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>334000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>331900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>335600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>323800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>333000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>303900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>350300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>343600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>341700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>333200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>335000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>344400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>337500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>327100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>323100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>328800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>341400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>378900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>386600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>384000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>383500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>346300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>344300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>345200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>353000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>352800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>661600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>340100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>337400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>339900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>339900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1349700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>576100</v>
+      </c>
+      <c r="F49" s="3">
         <v>587900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>554000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1184300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>574200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>542100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>542200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>545600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>521000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>543300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>527800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1143600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1178400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>951100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>963400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1007700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1075800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>936100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>926100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>910700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>923400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>945600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1044600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1034400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1071500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1088000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>956700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>976700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1013600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>972200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>935900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>931700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5316,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5435,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F52" s="3">
         <v>26600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>25400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>25000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>26500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>25400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>25800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>34900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>38800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>29100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>47800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>21100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>8700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>74600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>73000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>65500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>73200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>73500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>73500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>75800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>82700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>77000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>79500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>88400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>88100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>104000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>102600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>177500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>186700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>192900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>194100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5673,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2247800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2322200</v>
+      </c>
+      <c r="F54" s="3">
         <v>2243800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2058200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2003600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2202100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1699500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1741900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1875000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1855400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1674800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1700000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1872500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1818400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1655400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1627600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1694500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1750700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1563800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1580700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1618300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1563300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1687700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1805500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1852900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1930100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2117700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1903300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1835600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1914900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5839,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,686 +5882,724 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>437500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>337600</v>
+      </c>
+      <c r="F57" s="3">
         <v>368800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>286400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>372600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>291600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>209100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>183500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>202500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>224800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>180500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>167100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>298900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>330700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>282300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>268200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>257200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>296200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>239100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>215100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>202600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>223300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>263600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>254500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>207400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>233800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>326000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>247300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>238500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>244400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>346500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>270000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>238600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>264200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>248200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>232300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>219500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>361300</v>
+      </c>
+      <c r="F58" s="3">
         <v>227000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>275400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>270900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>312000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>46100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>181500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>340900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>250600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>136000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>252900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>271700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>132900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>137300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>128900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>131400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>80100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>82400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>75900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>76900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>8100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>5300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>9400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>5400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>7700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>7300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>11700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>7700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>11900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>7500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>3600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>8100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>246100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>318200</v>
+      </c>
+      <c r="F59" s="3">
         <v>325900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>250400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>224400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>328300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>276900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>161400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>206400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>278700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>247700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>194500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>227600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>220700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>213600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>178500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>198100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>249200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>155000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>146400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>176000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>204700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>214200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>137700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>209000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>285700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>273100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>218600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>178900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>300100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>238400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>99100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>157200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>262900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>279700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>141200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>204600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1082300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1114700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1028000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>898700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>867900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1050600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>625600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>603700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>842500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>853300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>669500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>720900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>798200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>684300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>633200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>575700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>586800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>625400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>476500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>437400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>455500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>431600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>485900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>397500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>425800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>524900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>606900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>468800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>424700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>547500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>596600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>376800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>407800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>535200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>535400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>377100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>432200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>651600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>657100</v>
+      </c>
+      <c r="F61" s="3">
         <v>657300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>657200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>655700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>656700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>655600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>655400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>655000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>654800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>654700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>648100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>706100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>742100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>682300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>610600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>595500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>607200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>580900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>559600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>555500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>592100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>638400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>692800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>668900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>717900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>715700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>656800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>663800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>650400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>629200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>590800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>619200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>623500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>649100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>679800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>692400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>248900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>291400</v>
+      </c>
+      <c r="F62" s="3">
         <v>284900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>239200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>228600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>286500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>228500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>242800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>243800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>249900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>205800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>194600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>224100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>262400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>176700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>178900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>206000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>205400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>168300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>131100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>132100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>138100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>134900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>164000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>129500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>127200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>207600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>173500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>149100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>145800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>220400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>189900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>181100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>172900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>189700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>146700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>150200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6711,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6830,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6949,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1991100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2071800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1978400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1803100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1757400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2003500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1516400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1510500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1752700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1767500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1542700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1570700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1728400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1688800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1492200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1365200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1388400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1438100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1225700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1128100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1143200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1161800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1259200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1254400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1224200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1370000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1530200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1299100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1237600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1343700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7115,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7230,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7349,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7468,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7587,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-462400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-467900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-468000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-435600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-419200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-412200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-390800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-343100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-255500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-270500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-249900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-240100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>78600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>67800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>101100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>202400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>259000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>265800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>292100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>409300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>435200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>363400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>410200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>511700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>570600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>522500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>540400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>553600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>554200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>518600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>498700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>556100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>565500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>590400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>577100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>562200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>582100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7825,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7944,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8063,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>256700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>250500</v>
+      </c>
+      <c r="F76" s="3">
         <v>265400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>255100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>246300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>198600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>183100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>231400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>122300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>87800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>132100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>129300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>144000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>129500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>163200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>262400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>306100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>312600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>338100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>452600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>475100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>401400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>428500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>551100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>628700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>560000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>587600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>604200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>598000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>571200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>552200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>629000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>624100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>649100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>626200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>602800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>615800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8301,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-34700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-45800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-90300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-31400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-33900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-34400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-19700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-133600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-21600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>74800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-35800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>47700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>10200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>35400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>8800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>8900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>31600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>23100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,121 +8591,129 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>5000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3900</v>
       </c>
       <c r="L83" s="3">
         <v>4300</v>
       </c>
       <c r="M83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>63700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>55800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>53400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>53300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>52400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>49200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>41400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>41200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>42300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>41800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>47000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>48000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>47600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>48900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>47000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>44300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>48100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>50100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>45800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>45300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>52300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>50400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>41500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>42900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>48800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8825,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8944,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9063,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9182,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9301,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F89" s="3">
         <v>137400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>28800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-79200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>159100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-19100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-59300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>26200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>138800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>66900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-80700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>52600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>28800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-39100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>80600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>30800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>32200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>73700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>35000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-20800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>212500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>29600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>151600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>130000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>27400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>23400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>231800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>52400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,121 +9467,129 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-14600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-21800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-13800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-32600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-104400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-20600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-75800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-12900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9701,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +9820,133 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-156900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-61700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-62200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-174900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-23800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-39000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-141000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-6900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-14200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-40000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-118700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-4900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-23100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-82100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-11500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-43600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-63200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-34400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-220100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-43100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-143500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>5300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9986,10 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9556,20 +10023,20 @@
       <c r="M96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-15300</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-13500</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-13500</v>
@@ -9578,7 +10045,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-13500</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -9587,55 +10054,61 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10220,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10339,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,343 +10458,367 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>138000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-68700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>75000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>267900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-141100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>48500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>76000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>121800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-127500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>130500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-14100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>49100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-14000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-13300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>69800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-14300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-15700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>3100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>3300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>5400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>12000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>8200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>5100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>9500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>9000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F102" s="3">
         <v>17700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-28900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-67600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>101900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>8300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-23000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>52800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>8900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-124100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>32500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-13900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-15200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>32200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>4900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>25400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>8800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-47200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-228200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>161000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>4600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-75400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>7200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>103800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>8300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>179500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>39400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-85500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MANU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>MANU</t>
   </si>
@@ -656,334 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E8" s="3">
         <v>256100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>188700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>224900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>207400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>248800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>191800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>179700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>172600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>287600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>191700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>212600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>210400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>219700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>183900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>151600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>189600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>230000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>160300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>116600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>141100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>202500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>128900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>99400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>164700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>229800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>184700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>185900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>202500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>275500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>178300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>157200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>190200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>231400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>187400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>229400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>167500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>207900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E9" s="3">
         <v>234100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>56700</v>
       </c>
-      <c r="G9" s="3">
-        <v>30900</v>
-      </c>
       <c r="H9" s="3">
+        <v>28200</v>
+      </c>
+      <c r="I9" s="3">
         <v>246000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>253000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>44400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1059,50 +1066,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E10" s="3">
         <v>22000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>168100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>168200</v>
       </c>
-      <c r="G10" s="3">
-        <v>176600</v>
-      </c>
       <c r="H10" s="3">
+        <v>179200</v>
+      </c>
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>171700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>138200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>153600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>191700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>168300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>177100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1178,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,70 +1476,73 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-60500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-36100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>37300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-36000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-5700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>18800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>12400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
@@ -1530,175 +1550,181 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>4600</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>25900</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>2500</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>-6300</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E15" s="3">
         <v>80200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>79300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>64800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>77100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>64000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>69600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>62200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>57400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>63700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>55800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>53300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>52400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>49200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>41400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>41200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>42300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>41800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>42400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>47600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>47000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>44300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>50100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>52300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>50400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>41500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>42900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>48800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>214600</v>
+      </c>
+      <c r="E17" s="3">
         <v>234100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>231700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>239900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>206000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>246000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>237200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>216700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>219000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>253000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>225500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>214800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>218600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>223400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>229400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>216700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>223400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>173100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>162200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>166800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>145700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>161000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>146900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>169100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>180000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>169700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>217300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>183500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>217400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>160000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>187500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>180800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>176400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>164000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>175800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>172900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>158300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>150200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E18" s="3">
         <v>22000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-45400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-77800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-45600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-25700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>56800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-47500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>49800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>58100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-30300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>55000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>23400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>53600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-5400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>49600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,603 +2051,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>16500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-22400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6500</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>-22500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>31500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>26600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-30500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-29900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>4400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>28800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-26700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>27300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E21" s="3">
         <v>102200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>72700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>70000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>104100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>65800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>58900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>86600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-54300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>56400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>30800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>128000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>124600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>60000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>65400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>104800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>68200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>61600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>108000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>79400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>98100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>39700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>89700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E22" s="3">
         <v>19800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>53200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6600</v>
-      </c>
-      <c r="U22" s="3">
-        <v>6700</v>
       </c>
       <c r="V22" s="3">
         <v>6700</v>
       </c>
       <c r="W22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="X22" s="3">
         <v>6100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>6900</v>
       </c>
       <c r="AA22" s="3">
         <v>6900</v>
       </c>
       <c r="AB22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AC22" s="3">
         <v>6500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>6400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>6700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>7000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>6500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>7100</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E23" s="3">
         <v>7600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-43200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-52500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-105500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-44000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-117500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-25100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-52200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>79800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-56800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>70600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-42500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>49700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>49300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>22300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>49600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>33800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-15200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-10100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-26900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-10200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-8500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>11100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>9900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>18000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-4800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>10700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E26" s="3">
         <v>5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-90300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-33900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-90700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-19700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-53700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>84000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-45500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>53200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>35400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>38200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>12500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>31600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>23100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-90300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-33900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-90700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-19700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-53700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>84000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-45500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>53200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>35400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>38200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>12500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>31600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>23100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,14 +3191,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3149,31 +3210,31 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-79900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-2700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -3181,21 +3242,21 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-63900</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-16500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>22400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6500</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>22500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-31500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>30500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>29900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-4400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>26700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>11200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>8700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-90300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-33900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-90700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-19700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-133600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>74800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-35800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>47700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>35400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-25700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>31600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>23100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-90300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-33900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-90700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-19700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-133600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>74800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-35800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>47700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>35400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-25700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>31600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>23100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E41" s="3">
         <v>59800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>118000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>119600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>96600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>155100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>125000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>101000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>94400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>69700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>62900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>120100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>137500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>191300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>435300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>258100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>251500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>326900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>312900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>209100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>202600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>282000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>378600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>201000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>161600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>216300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,20 +4368,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5300</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4370,484 +4460,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>236900</v>
+      </c>
+      <c r="E43" s="3">
         <v>236300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>177300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>228700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>214100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>188600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>117000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>118000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>185000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>107300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>114000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>160400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>232000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>132900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>117200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>129200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>156100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>107000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>114800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>101500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>152600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>116300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>199300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>113300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>144100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>125300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>92300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>247800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>164900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>122400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>218300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>152200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>160500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>111200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>135300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>114100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>163800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E44" s="3">
         <v>25300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3500</v>
-      </c>
-      <c r="AH44" s="3">
-        <v>1800</v>
       </c>
       <c r="AI44" s="3">
         <v>1800</v>
       </c>
       <c r="AJ44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AK44" s="3">
         <v>2500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>55100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>21000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>18000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>21400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>18900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>6000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>359900</v>
+      </c>
+      <c r="E46" s="3">
         <v>348400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>344500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>389100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>349400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>359800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>383100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>224000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>231000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>307600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>264700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>282700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>321600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>223800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>303500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>278400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>295400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>269900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>264200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>221400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>271400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>215800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>274200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>252100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>303100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>341700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>549500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>509300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>420600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>453500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>534500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>366700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>369100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>399100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>520200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>322100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>332900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>315500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4884,327 +4989,336 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>4700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>27900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>24700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>38100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>50900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>25300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>31500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>40200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>29700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>53300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>56500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>55400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>57100</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>14000</v>
       </c>
       <c r="AE47" s="3">
         <v>14000</v>
       </c>
       <c r="AF47" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AG47" s="3">
         <v>14400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>14100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>16200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>13000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>20100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>19700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>395300</v>
+      </c>
+      <c r="E48" s="3">
         <v>405200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>411600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>410300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>371300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>343900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>366400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>334000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>331900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>335600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>323800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>333000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>303900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>350300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>343600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>341700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>333200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>335000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>344400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>337500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>327100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>323100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>328800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>341400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>378900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>386600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>384000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>383500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>346300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>344300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>345200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>353000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>352800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>661600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>340100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>337400</v>
-      </c>
-      <c r="AM48" s="3">
-        <v>339900</v>
       </c>
       <c r="AN48" s="3">
         <v>339900</v>
       </c>
       <c r="AO48" s="3">
+        <v>339900</v>
+      </c>
+      <c r="AP48" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>565900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1349700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>576100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>587900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>554000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1184300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>574200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>542100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>542200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>545600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>521000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>543300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>527800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1143600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1178400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>951100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>963400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1007700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1075800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>936100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>926100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>910700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>923400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>945600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1044600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1034400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1071500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1088000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>956700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>976700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1013600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1033800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>972200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2008800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1050900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>935900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>931700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1018200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1053800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26000</v>
+        <v>25500</v>
       </c>
       <c r="E52" s="3">
         <v>26000</v>
       </c>
       <c r="F52" s="3">
+        <v>26000</v>
+      </c>
+      <c r="G52" s="3">
         <v>26600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>47800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>74600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>73000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>65500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>73200</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>73500</v>
       </c>
       <c r="AB52" s="3">
         <v>73500</v>
       </c>
       <c r="AC52" s="3">
+        <v>73500</v>
+      </c>
+      <c r="AD52" s="3">
         <v>75800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>82700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>77000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>79500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>88400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>88100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>102600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>177500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>186700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>192900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>194100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2100200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2247800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2322200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2243800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2058200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2003600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2202100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1699500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1741900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1875000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1855400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1674800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1700000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1872500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1818400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1655400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1627600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1694500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1750700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1563800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1580700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1618300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1563300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1687700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1805500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1852900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1930100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2117700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1903300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1835600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1914900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1998400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1786500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1832200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1980600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2000400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1806400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1890700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1915000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>310200</v>
+      </c>
+      <c r="E57" s="3">
         <v>437500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>337600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>368800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>286400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>372600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>291600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>209100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>183500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>202500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>224800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>180500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>167100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>298900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>330700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>282300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>268200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>257200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>296200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>239100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>215100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>202600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>223300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>263600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>254500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>207400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>233800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>326000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>247300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>238500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>244400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>346500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>238600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>264200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>248200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>232300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>219500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>347200</v>
+      </c>
+      <c r="E58" s="3">
         <v>398700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>361300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>227000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>275400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>270900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>312000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>181500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>340900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>250600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>136000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>252900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>271700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>132900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>137300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>128900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>131400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>80100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>82400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>75900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>76900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>9400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>11700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>11900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>8100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>7500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>8100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>206600</v>
+      </c>
+      <c r="E59" s="3">
         <v>246100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>318200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>325900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>250400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>224400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>328300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>276900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>161400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>206400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>278700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>247700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>194500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>227600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>220700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>213600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>178500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>198100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>249200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>155000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>146400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>176000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>204700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>214200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>137700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>209000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>285700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>273100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>218600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>178900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>300100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>238400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>99100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>157200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>262900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>279700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>141200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>204600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>968800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1082300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1114700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1028000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>898700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>867900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1050600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>625600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>603700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>842500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>853300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>669500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>720900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>798200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>684300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>633200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>575700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>586800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>625400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>476500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>437400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>455500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>431600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>485900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>397500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>425800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>524900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>606900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>468800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>424700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>547500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>596600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>376800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>407800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>535200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>535400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>377100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>432200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>494800</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E61" s="3">
         <v>651600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>657100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>657300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>657200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>655700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>656700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>655600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>655400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>655000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>654800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>654700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>648100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>706100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>742100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>682300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>610600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>595500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>607200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>580900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>559600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>555500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>592100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>638400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>692800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>668900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>717900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>715700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>656800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>663800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>650400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>629200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>590800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>619200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>623500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>649100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>679800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>692400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>657500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E62" s="3">
         <v>248900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>291400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>284900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>239200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>228600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>286500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>228500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>242800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>243800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>249900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>205800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>194600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>224100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>262400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>176700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>178900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>206000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>205400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>168300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>131100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>132100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>138100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>134900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>164000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>129500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>127200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>207600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>173500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>149100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>145800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>220400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>189900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>181100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>172900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>189700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>146700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>150200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1863300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1991100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2071800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1978400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1803100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1757400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2003500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1516400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1510500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1752700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1767500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1542700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1570700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1728400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1688800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1492200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1365200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1388400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1438100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1225700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1128100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1143200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1161800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1259200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1254400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1224200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1370000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1530200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1299100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1237600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1343700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1446200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1157500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1208100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1331600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1374200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1203600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1274800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1315500</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-468900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-462400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-467900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-468000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-435600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-419200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-412200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-390800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-343100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-255500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-270500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-249900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-240100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>67800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>101100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>202400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>259000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>265800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>292100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>409300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>435200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>363400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>410200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>511700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>570600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>522500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>540400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>553600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>554200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>518600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>498700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>556100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>565500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>590400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>577100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>562200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>582100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>558300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>236900</v>
+      </c>
+      <c r="E76" s="3">
         <v>256700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>250500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>265400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>255100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>246300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>198600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>183100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>231400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>122300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>87800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>132100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>129300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>129500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>163200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>262400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>306100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>312600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>338100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>452600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>475100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>401400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>428500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>551100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>628700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>560000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>587600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>604200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>598000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>571200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>552200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>629000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>624100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>649100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>626200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>602800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>615800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>599500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-90300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-33900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-90700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-19700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-133600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>74800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-35800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>47700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-31400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>35400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-25700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>31600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>23100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>5200</v>
       </c>
       <c r="G83" s="3">
         <v>5200</v>
       </c>
       <c r="H83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I83" s="3">
         <v>5300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4300</v>
       </c>
       <c r="L83" s="3">
         <v>4300</v>
       </c>
       <c r="M83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>53400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>53300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>52400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>49200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>41400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>41200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>42300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>41800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>47000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>50100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>45800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>52300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>50400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>41500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>42900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>48800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>43700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>137400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-79200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>159100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-59300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>138800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-80700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>52600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-39100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>80600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>73700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>212500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>29600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>151600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>130000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-57900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>23400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>231800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>52400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-55900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-104400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-75800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-9900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-211200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-156900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-62200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-174900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-141000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-118700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-82100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-63200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-34400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-220100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-43100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-143500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-21300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-31700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>5300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-164500</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,8 +10221,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10029,27 +10263,27 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-15300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-13500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-13500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10060,11 +10294,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-14500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -10072,11 +10306,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10084,11 +10318,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10096,19 +10330,22 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-15000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-15600</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E100" s="3">
         <v>31900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>138000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-68700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>75000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>267900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-141100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>48500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>76000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>121800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-127500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>130500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>49100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-13300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>69800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-37300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-20100</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-500</v>
       </c>
       <c r="AC100" s="3">
         <v>-500</v>
       </c>
       <c r="AD100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-14400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-14300</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>-100</v>
       </c>
       <c r="AK100" s="3">
         <v>-100</v>
       </c>
       <c r="AL100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-15100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-15700</v>
-      </c>
-      <c r="AN100" s="3">
-        <v>-100</v>
       </c>
       <c r="AO100" s="3">
         <v>-100</v>
       </c>
+      <c r="AP100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>12000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-2500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>9000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>101900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-124100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>25400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>8800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-47200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-228200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>161000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-75400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>7200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>103800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-79500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-96600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>179500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>39400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-54700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-85500</v>
       </c>
     </row>
